--- a/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
+++ b/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
@@ -957,6 +957,12 @@
       <c r="C2" t="n">
         <v>65.04000000000001</v>
       </c>
+      <c r="D2" t="n">
+        <v>0.008813068626653387</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0212968195055388</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -968,13 +974,11 @@
       <c r="C3" t="n">
         <v>66.44</v>
       </c>
-      <c r="D3">
-        <f>LN(B3/B2)</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>LN(C3/C2)</f>
-        <v/>
+      <c r="D3" t="n">
+        <v>-0.003264457418942081</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.01516559245060246</v>
       </c>
     </row>
     <row r="4">
@@ -987,13 +991,11 @@
       <c r="C4" t="n">
         <v>65.44</v>
       </c>
-      <c r="D4">
-        <f>LN(B4/B3)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>LN(C4/C3)</f>
-        <v/>
+      <c r="D4" t="n">
+        <v>0.009818883705038944</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02071907764289431</v>
       </c>
     </row>
     <row r="5">
@@ -1006,13 +1008,11 @@
       <c r="C5" t="n">
         <v>66.81</v>
       </c>
-      <c r="D5">
-        <f>LN(B5/B4)</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>LN(C5/C4)</f>
-        <v/>
+      <c r="D5" t="n">
+        <v>0.001568343333675865</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01293794536058205</v>
       </c>
     </row>
     <row r="6">
@@ -1025,13 +1025,11 @@
       <c r="C6" t="n">
         <v>67.68000000000001</v>
       </c>
-      <c r="D6">
-        <f>LN(B6/B5)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>LN(C6/C5)</f>
-        <v/>
+      <c r="D6" t="n">
+        <v>0.007249770854574006</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01626767023995492</v>
       </c>
     </row>
     <row r="7">
@@ -1044,13 +1042,11 @@
       <c r="C7" t="n">
         <v>68.79000000000001</v>
       </c>
-      <c r="D7">
-        <f>LN(B7/B6)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>LN(C7/C6)</f>
-        <v/>
+      <c r="D7" t="n">
+        <v>0.016407202460669</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01543485384076314</v>
       </c>
     </row>
     <row r="8">
@@ -1063,13 +1059,11 @@
       <c r="C8" t="n">
         <v>69.86</v>
       </c>
-      <c r="D8">
-        <f>LN(B8/B7)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>LN(C8/C7)</f>
-        <v/>
+      <c r="D8" t="n">
+        <v>0.00581933283845353</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03640342938800557</v>
       </c>
     </row>
     <row r="9">
@@ -1082,13 +1076,11 @@
       <c r="C9" t="n">
         <v>72.45</v>
       </c>
-      <c r="D9">
-        <f>LN(B9/B8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>LN(C9/C8)</f>
-        <v/>
+      <c r="D9" t="n">
+        <v>-0.001596943598473373</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02602149408655188</v>
       </c>
     </row>
     <row r="10">
@@ -1101,13 +1093,11 @@
       <c r="C10" t="n">
         <v>74.36</v>
       </c>
-      <c r="D10">
-        <f>LN(B10/B9)</f>
-        <v/>
-      </c>
-      <c r="E10">
-        <f>LN(C10/C9)</f>
-        <v/>
+      <c r="D10" t="n">
+        <v>0.009384395506698995</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04239149915857789</v>
       </c>
     </row>
     <row r="11">
@@ -1120,13 +1110,11 @@
       <c r="C11" t="n">
         <v>77.58</v>
       </c>
-      <c r="D11">
-        <f>LN(B11/B10)</f>
-        <v/>
-      </c>
-      <c r="E11">
-        <f>LN(C11/C10)</f>
-        <v/>
+      <c r="D11" t="n">
+        <v>0.01949122883380944</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02670895126452178</v>
       </c>
     </row>
     <row r="12">
@@ -1139,13 +1127,11 @@
       <c r="C12" t="n">
         <v>79.68000000000001</v>
       </c>
-      <c r="D12">
-        <f>LN(B12/B11)</f>
-        <v/>
-      </c>
-      <c r="E12">
-        <f>LN(C12/C11)</f>
-        <v/>
+      <c r="D12" t="n">
+        <v>-0.01030938522023828</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.001255808277560342</v>
       </c>
     </row>
     <row r="13">
@@ -1158,13 +1144,11 @@
       <c r="C13" t="n">
         <v>79.58</v>
       </c>
-      <c r="D13">
-        <f>LN(B13/B12)</f>
-        <v/>
-      </c>
-      <c r="E13">
-        <f>LN(C13/C12)</f>
-        <v/>
+      <c r="D13" t="n">
+        <v>-0.02145462058649753</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.02803445572641574</v>
       </c>
     </row>
     <row r="14">
@@ -1177,13 +1161,11 @@
       <c r="C14" t="n">
         <v>77.38</v>
       </c>
-      <c r="D14">
-        <f>LN(B14/B13)</f>
-        <v/>
-      </c>
-      <c r="E14">
-        <f>LN(C14/C13)</f>
-        <v/>
+      <c r="D14" t="n">
+        <v>0.03119020217903341</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03342327758966579</v>
       </c>
     </row>
     <row r="15">
@@ -1196,13 +1178,11 @@
       <c r="C15" t="n">
         <v>80.01000000000001</v>
       </c>
-      <c r="D15">
-        <f>LN(B15/B14)</f>
-        <v/>
-      </c>
-      <c r="E15">
-        <f>LN(C15/C14)</f>
-        <v/>
+      <c r="D15" t="n">
+        <v>0.01563866591363505</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01525610985015118</v>
       </c>
     </row>
     <row r="16">
@@ -1215,13 +1195,11 @@
       <c r="C16" t="n">
         <v>81.23999999999999</v>
       </c>
-      <c r="D16">
-        <f>LN(B16/B15)</f>
-        <v/>
-      </c>
-      <c r="E16">
-        <f>LN(C16/C15)</f>
-        <v/>
+      <c r="D16" t="n">
+        <v>-0.01262611836459297</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.03737111992991739</v>
       </c>
     </row>
     <row r="17">
@@ -1234,13 +1212,11 @@
       <c r="C17" t="n">
         <v>78.26000000000001</v>
       </c>
-      <c r="D17">
-        <f>LN(B17/B16)</f>
-        <v/>
-      </c>
-      <c r="E17">
-        <f>LN(C17/C16)</f>
-        <v/>
+      <c r="D17" t="n">
+        <v>-0.1220622706642805</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1355413700951207</v>
       </c>
     </row>
     <row r="18">
@@ -1253,13 +1229,11 @@
       <c r="C18" t="n">
         <v>68.34</v>
       </c>
-      <c r="D18">
-        <f>LN(B18/B17)</f>
-        <v/>
-      </c>
-      <c r="E18">
-        <f>LN(C18/C17)</f>
-        <v/>
+      <c r="D18" t="n">
+        <v>0.006124957772197905</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0557754790323485</v>
       </c>
     </row>
     <row r="19">
@@ -1272,13 +1246,11 @@
       <c r="C19" t="n">
         <v>72.26000000000001</v>
       </c>
-      <c r="D19">
-        <f>LN(B19/B18)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>LN(C19/C18)</f>
-        <v/>
+      <c r="D19" t="n">
+        <v>-0.09203466655513794</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.03908786839325835</v>
       </c>
     </row>
     <row r="20">
@@ -1291,13 +1263,11 @@
       <c r="C20" t="n">
         <v>69.48999999999999</v>
       </c>
-      <c r="D20">
-        <f>LN(B20/B19)</f>
-        <v/>
-      </c>
-      <c r="E20">
-        <f>LN(C20/C19)</f>
-        <v/>
+      <c r="D20" t="n">
+        <v>-0.1622789791528936</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.1927077287625898</v>
       </c>
     </row>
     <row r="21">
@@ -1310,13 +1280,11 @@
       <c r="C21" t="n">
         <v>57.31</v>
       </c>
-      <c r="D21">
-        <f>LN(B21/B20)</f>
-        <v/>
-      </c>
-      <c r="E21">
-        <f>LN(C21/C20)</f>
-        <v/>
+      <c r="D21" t="n">
+        <v>0.0976966850944738</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.07769104598141062</v>
       </c>
     </row>
     <row r="22">
@@ -1329,13 +1297,11 @@
       <c r="C22" t="n">
         <v>61.94</v>
       </c>
-      <c r="D22">
-        <f>LN(B22/B21)</f>
-        <v/>
-      </c>
-      <c r="E22">
-        <f>LN(C22/C21)</f>
-        <v/>
+      <c r="D22" t="n">
+        <v>-0.02100225900708992</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.02600522700151621</v>
       </c>
     </row>
     <row r="23">
@@ -1348,13 +1314,11 @@
       <c r="C23" t="n">
         <v>60.35</v>
       </c>
-      <c r="D23">
-        <f>LN(B23/B22)</f>
-        <v/>
-      </c>
-      <c r="E23">
-        <f>LN(C23/C22)</f>
-        <v/>
+      <c r="D23" t="n">
+        <v>0.1142366828476501</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1045316718474255</v>
       </c>
     </row>
     <row r="24">
@@ -1367,13 +1331,11 @@
       <c r="C24" t="n">
         <v>67</v>
       </c>
-      <c r="D24">
-        <f>LN(B24/B23)</f>
-        <v/>
-      </c>
-      <c r="E24">
-        <f>LN(C24/C23)</f>
-        <v/>
+      <c r="D24" t="n">
+        <v>0.02992254143571757</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.05375295351156097</v>
       </c>
     </row>
     <row r="25">
@@ -1386,13 +1348,11 @@
       <c r="C25" t="n">
         <v>70.7</v>
       </c>
-      <c r="D25">
-        <f>LN(B25/B24)</f>
-        <v/>
-      </c>
-      <c r="E25">
-        <f>LN(C25/C24)</f>
-        <v/>
+      <c r="D25" t="n">
+        <v>-0.01324411353679196</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0005656108748073297</v>
       </c>
     </row>
     <row r="26">
@@ -1405,13 +1365,11 @@
       <c r="C26" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="D26">
-        <f>LN(B26/B25)</f>
-        <v/>
-      </c>
-      <c r="E26">
-        <f>LN(C26/C25)</f>
-        <v/>
+      <c r="D26" t="n">
+        <v>-0.002127941940515928</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.02139792151755507</v>
       </c>
     </row>
     <row r="27">
@@ -1424,13 +1382,11 @@
       <c r="C27" t="n">
         <v>72.27</v>
       </c>
-      <c r="D27">
-        <f>LN(B27/B26)</f>
-        <v/>
-      </c>
-      <c r="E27">
-        <f>LN(C27/C26)</f>
-        <v/>
+      <c r="D27" t="n">
+        <v>0.03440659773213572</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.07025585293597812</v>
       </c>
     </row>
     <row r="28">
@@ -1443,13 +1399,11 @@
       <c r="C28" t="n">
         <v>77.53</v>
       </c>
-      <c r="D28">
-        <f>LN(B28/B27)</f>
-        <v/>
-      </c>
-      <c r="E28">
-        <f>LN(C28/C27)</f>
-        <v/>
+      <c r="D28" t="n">
+        <v>-0.02281966630500351</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.007769040760024274</v>
       </c>
     </row>
     <row r="29">
@@ -1462,13 +1416,11 @@
       <c r="C29" t="n">
         <v>76.93000000000001</v>
       </c>
-      <c r="D29">
-        <f>LN(B29/B28)</f>
-        <v/>
-      </c>
-      <c r="E29">
-        <f>LN(C29/C28)</f>
-        <v/>
+      <c r="D29" t="n">
+        <v>0.03153642851942037</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.03562457787375062</v>
       </c>
     </row>
     <row r="30">
@@ -1481,13 +1433,11 @@
       <c r="C30" t="n">
         <v>79.72</v>
       </c>
-      <c r="D30">
-        <f>LN(B30/B29)</f>
-        <v/>
-      </c>
-      <c r="E30">
-        <f>LN(C30/C29)</f>
-        <v/>
+      <c r="D30" t="n">
+        <v>0.02962335097080689</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.002889267759572742</v>
       </c>
     </row>
     <row r="31">
@@ -1500,13 +1450,11 @@
       <c r="C31" t="n">
         <v>79.48999999999999</v>
       </c>
-      <c r="D31">
-        <f>LN(B31/B30)</f>
-        <v/>
-      </c>
-      <c r="E31">
-        <f>LN(C31/C30)</f>
-        <v/>
+      <c r="D31" t="n">
+        <v>0.04797785896122955</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.04176255092615157</v>
       </c>
     </row>
     <row r="32">
@@ -1519,13 +1467,11 @@
       <c r="C32" t="n">
         <v>82.88</v>
       </c>
-      <c r="D32">
-        <f>LN(B32/B31)</f>
-        <v/>
-      </c>
-      <c r="E32">
-        <f>LN(C32/C31)</f>
-        <v/>
+      <c r="D32" t="n">
+        <v>-0.04896378980903639</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.02172182314683597</v>
       </c>
     </row>
     <row r="33">
@@ -1538,13 +1484,11 @@
       <c r="C33" t="n">
         <v>84.7</v>
       </c>
-      <c r="D33">
-        <f>LN(B33/B32)</f>
-        <v/>
-      </c>
-      <c r="E33">
-        <f>LN(C33/C32)</f>
-        <v/>
+      <c r="D33" t="n">
+        <v>0.01838446970884191</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.03172287153479104</v>
       </c>
     </row>
     <row r="34">
@@ -1557,13 +1501,11 @@
       <c r="C34" t="n">
         <v>87.43000000000001</v>
       </c>
-      <c r="D34">
-        <f>LN(B34/B33)</f>
-        <v/>
-      </c>
-      <c r="E34">
-        <f>LN(C34/C33)</f>
-        <v/>
+      <c r="D34" t="n">
+        <v>-0.02904839903372284</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.01114661222491342</v>
       </c>
     </row>
     <row r="35">
@@ -1576,13 +1518,11 @@
       <c r="C35" t="n">
         <v>88.41</v>
       </c>
-      <c r="D35">
-        <f>LN(B35/B34)</f>
-        <v/>
-      </c>
-      <c r="E35">
-        <f>LN(C35/C34)</f>
-        <v/>
+      <c r="D35" t="n">
+        <v>0.03941178510906874</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02920403709948452</v>
       </c>
     </row>
     <row r="36">
@@ -1595,13 +1535,11 @@
       <c r="C36" t="n">
         <v>91.03</v>
       </c>
-      <c r="D36">
-        <f>LN(B36/B35)</f>
-        <v/>
-      </c>
-      <c r="E36">
-        <f>LN(C36/C35)</f>
-        <v/>
+      <c r="D36" t="n">
+        <v>0.01742864837982932</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05232538820206139</v>
       </c>
     </row>
     <row r="37">
@@ -1614,13 +1552,11 @@
       <c r="C37" t="n">
         <v>95.92</v>
       </c>
-      <c r="D37">
-        <f>LN(B37/B36)</f>
-        <v/>
-      </c>
-      <c r="E37">
-        <f>LN(C37/C36)</f>
-        <v/>
+      <c r="D37" t="n">
+        <v>0.01238437799774403</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.004265286050273322</v>
       </c>
     </row>
     <row r="38">
@@ -1633,13 +1569,11 @@
       <c r="C38" t="n">
         <v>96.33</v>
       </c>
-      <c r="D38">
-        <f>LN(B38/B37)</f>
-        <v/>
-      </c>
-      <c r="E38">
-        <f>LN(C38/C37)</f>
-        <v/>
+      <c r="D38" t="n">
+        <v>-0.002825930865964706</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.03938266958735458</v>
       </c>
     </row>
     <row r="39">
@@ -1652,13 +1586,11 @@
       <c r="C39" t="n">
         <v>92.61</v>
       </c>
-      <c r="D39">
-        <f>LN(B39/B38)</f>
-        <v/>
-      </c>
-      <c r="E39">
-        <f>LN(C39/C38)</f>
-        <v/>
+      <c r="D39" t="n">
+        <v>0.01710913896532236</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1374917938406196</v>
       </c>
     </row>
     <row r="40">
@@ -1671,13 +1603,11 @@
       <c r="C40" t="n">
         <v>106.26</v>
       </c>
-      <c r="D40">
-        <f>LN(B40/B39)</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>LN(C40/C39)</f>
-        <v/>
+      <c r="D40" t="n">
+        <v>0.0242099284995213</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.04463178057312001</v>
       </c>
     </row>
     <row r="41">
@@ -1690,13 +1620,11 @@
       <c r="C41" t="n">
         <v>111.11</v>
       </c>
-      <c r="D41">
-        <f>LN(B41/B40)</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>LN(C41/C40)</f>
-        <v/>
+      <c r="D41" t="n">
+        <v>0.006415721881558568</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.03362851167362502</v>
       </c>
     </row>
     <row r="42">
@@ -1709,13 +1637,11 @@
       <c r="C42" t="n">
         <v>114.91</v>
       </c>
-      <c r="D42">
-        <f>LN(B42/B41)</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>LN(C42/C41)</f>
-        <v/>
+      <c r="D42" t="n">
+        <v>0.007181704158801012</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.07911178039610746</v>
       </c>
     </row>
     <row r="43">
@@ -1728,13 +1654,11 @@
       <c r="C43" t="n">
         <v>124.37</v>
       </c>
-      <c r="D43">
-        <f>LN(B43/B42)</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>LN(C43/C42)</f>
-        <v/>
+      <c r="D43" t="n">
+        <v>0.03210913668106233</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.003531587264712668</v>
       </c>
     </row>
     <row r="44">
@@ -1747,13 +1671,11 @@
       <c r="C44" t="n">
         <v>124.81</v>
       </c>
-      <c r="D44">
-        <f>LN(B44/B43)</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>LN(C44/C43)</f>
-        <v/>
+      <c r="D44" t="n">
+        <v>-0.02337535432499913</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.0313326684991395</v>
       </c>
     </row>
     <row r="45">
@@ -1766,13 +1688,11 @@
       <c r="C45" t="n">
         <v>120.96</v>
       </c>
-      <c r="D45">
-        <f>LN(B45/B44)</f>
-        <v/>
-      </c>
-      <c r="E45">
-        <f>LN(C45/C44)</f>
-        <v/>
+      <c r="D45" t="n">
+        <v>-0.02541238682120831</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.07696104113612832</v>
       </c>
     </row>
     <row r="46">
@@ -1785,13 +1705,11 @@
       <c r="C46" t="n">
         <v>112</v>
       </c>
-      <c r="D46">
-        <f>LN(B46/B45)</f>
-        <v/>
-      </c>
-      <c r="E46">
-        <f>LN(C46/C45)</f>
-        <v/>
+      <c r="D46" t="n">
+        <v>-0.00645605235621415</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.04716648305333439</v>
       </c>
     </row>
     <row r="47">
@@ -1804,13 +1722,11 @@
       <c r="C47" t="n">
         <v>106.84</v>
       </c>
-      <c r="D47">
-        <f>LN(B47/B46)</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>LN(C47/C46)</f>
-        <v/>
+      <c r="D47" t="n">
+        <v>-0.006349438747599332</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.04966336325192159</v>
       </c>
     </row>
     <row r="48">
@@ -1823,13 +1739,11 @@
       <c r="C48" t="n">
         <v>112.28</v>
       </c>
-      <c r="D48">
-        <f>LN(B48/B47)</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>LN(C48/C47)</f>
-        <v/>
+      <c r="D48" t="n">
+        <v>0.01503887285348241</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.006569042708015536</v>
       </c>
     </row>
     <row r="49">
@@ -1842,13 +1756,11 @@
       <c r="C49" t="n">
         <v>113.02</v>
       </c>
-      <c r="D49">
-        <f>LN(B49/B48)</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>LN(C49/C48)</f>
-        <v/>
+      <c r="D49" t="n">
+        <v>0.03771267514366752</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.03435269746091846</v>
       </c>
     </row>
     <row r="50">
@@ -1861,13 +1773,11 @@
       <c r="C50" t="n">
         <v>116.97</v>
       </c>
-      <c r="D50">
-        <f>LN(B50/B49)</f>
-        <v/>
-      </c>
-      <c r="E50">
-        <f>LN(C50/C49)</f>
-        <v/>
+      <c r="D50" t="n">
+        <v>0.00191928160580628</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01737405455409044</v>
       </c>
     </row>
     <row r="51">
@@ -1880,13 +1790,11 @@
       <c r="C51" t="n">
         <v>119.02</v>
       </c>
-      <c r="D51">
-        <f>LN(B51/B50)</f>
-        <v/>
-      </c>
-      <c r="E51">
-        <f>LN(C51/C50)</f>
-        <v/>
+      <c r="D51" t="n">
+        <v>-0.005301342065264879</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.03401165224396936</v>
       </c>
     </row>
     <row r="52">
@@ -1899,13 +1807,11 @@
       <c r="C52" t="n">
         <v>115.04</v>
       </c>
-      <c r="D52">
-        <f>LN(B52/B51)</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>LN(C52/C51)</f>
-        <v/>
+      <c r="D52" t="n">
+        <v>-0.05804742800223844</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.05521724096668267</v>
       </c>
     </row>
     <row r="53">
@@ -1918,13 +1824,11 @@
       <c r="C53" t="n">
         <v>108.86</v>
       </c>
-      <c r="D53">
-        <f>LN(B53/B52)</f>
-        <v/>
-      </c>
-      <c r="E53">
-        <f>LN(C53/C52)</f>
-        <v/>
+      <c r="D53" t="n">
+        <v>0.0706787281712638</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.08645239906235995</v>
       </c>
     </row>
     <row r="54">
@@ -1937,13 +1841,11 @@
       <c r="C54" t="n">
         <v>118.69</v>
       </c>
-      <c r="D54">
-        <f>LN(B54/B53)</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>LN(C54/C53)</f>
-        <v/>
+      <c r="D54" t="n">
+        <v>0.0213438335907504</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.004790931626546032</v>
       </c>
     </row>
     <row r="55">
@@ -1956,13 +1858,11 @@
       <c r="C55" t="n">
         <v>119.26</v>
       </c>
-      <c r="D55">
-        <f>LN(B55/B54)</f>
-        <v/>
-      </c>
-      <c r="E55">
-        <f>LN(C55/C54)</f>
-        <v/>
+      <c r="D55" t="n">
+        <v>-0.007731019410779703</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.01623028019724603</v>
       </c>
     </row>
     <row r="56">
@@ -1975,13 +1875,11 @@
       <c r="C56" t="n">
         <v>117.34</v>
       </c>
-      <c r="D56">
-        <f>LN(B56/B55)</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>LN(C56/C55)</f>
-        <v/>
+      <c r="D56" t="n">
+        <v>0.02246098740566626</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.006412196552513792</v>
       </c>
     </row>
     <row r="57">
@@ -1994,13 +1892,11 @@
       <c r="C57" t="n">
         <v>116.59</v>
       </c>
-      <c r="D57">
-        <f>LN(B57/B56)</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>LN(C57/C56)</f>
-        <v/>
+      <c r="D57" t="n">
+        <v>0.01656467134909308</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.0474046214097814</v>
       </c>
     </row>
     <row r="58">
@@ -2013,13 +1909,11 @@
       <c r="C58" t="n">
         <v>122.25</v>
       </c>
-      <c r="D58">
-        <f>LN(B58/B57)</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>LN(C58/C57)</f>
-        <v/>
+      <c r="D58" t="n">
+        <v>-0.009686897486703379</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001307937732439714</v>
       </c>
     </row>
     <row r="59">
@@ -2032,13 +1926,11 @@
       <c r="C59" t="n">
         <v>122.41</v>
       </c>
-      <c r="D59">
-        <f>LN(B59/B58)</f>
-        <v/>
-      </c>
-      <c r="E59">
-        <f>LN(C59/C58)</f>
-        <v/>
+      <c r="D59" t="n">
+        <v>0.0124647782854589</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.03405131036026317</v>
       </c>
     </row>
     <row r="60">
@@ -2051,13 +1943,11 @@
       <c r="C60" t="n">
         <v>126.65</v>
       </c>
-      <c r="D60">
-        <f>LN(B60/B59)</f>
-        <v/>
-      </c>
-      <c r="E60">
-        <f>LN(C60/C59)</f>
-        <v/>
+      <c r="D60" t="n">
+        <v>-0.001713329444400377</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.04114724758105383</v>
       </c>
     </row>
     <row r="61">
@@ -2070,13 +1960,11 @@
       <c r="C61" t="n">
         <v>131.97</v>
       </c>
-      <c r="D61">
-        <f>LN(B61/B60)</f>
-        <v/>
-      </c>
-      <c r="E61">
-        <f>LN(C61/C60)</f>
-        <v/>
+      <c r="D61" t="n">
+        <v>0.01421369314127096</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.005440956519606923</v>
       </c>
     </row>
     <row r="62">
@@ -2089,13 +1977,11 @@
       <c r="C62" t="n">
         <v>132.69</v>
       </c>
-      <c r="D62">
-        <f>LN(B62/B61)</f>
-        <v/>
-      </c>
-      <c r="E62">
-        <f>LN(C62/C61)</f>
-        <v/>
+      <c r="D62" t="n">
+        <v>0.01810160562801328</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-0.004834941805203742</v>
       </c>
     </row>
     <row r="63">
@@ -2108,13 +1994,11 @@
       <c r="C63" t="n">
         <v>132.05</v>
       </c>
-      <c r="D63">
-        <f>LN(B63/B62)</f>
-        <v/>
-      </c>
-      <c r="E63">
-        <f>LN(C63/C62)</f>
-        <v/>
+      <c r="D63" t="n">
+        <v>-0.01486410093957471</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.03789179723487862</v>
       </c>
     </row>
     <row r="64">
@@ -2127,13 +2011,11 @@
       <c r="C64" t="n">
         <v>127.14</v>
       </c>
-      <c r="D64">
-        <f>LN(B64/B63)</f>
-        <v/>
-      </c>
-      <c r="E64">
-        <f>LN(C64/C63)</f>
-        <v/>
+      <c r="D64" t="n">
+        <v>0.01924440313712323</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.0896885619822568</v>
       </c>
     </row>
     <row r="65">
@@ -2146,13 +2028,11 @@
       <c r="C65" t="n">
         <v>139.07</v>
       </c>
-      <c r="D65">
-        <f>LN(B65/B64)</f>
-        <v/>
-      </c>
-      <c r="E65">
-        <f>LN(C65/C64)</f>
-        <v/>
+      <c r="D65" t="n">
+        <v>-0.03368102464750403</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.05247855713013875</v>
       </c>
     </row>
     <row r="66">
@@ -2165,13 +2045,11 @@
       <c r="C66" t="n">
         <v>131.96</v>
       </c>
-      <c r="D66">
-        <f>LN(B66/B65)</f>
-        <v/>
-      </c>
-      <c r="E66">
-        <f>LN(C66/C65)</f>
-        <v/>
+      <c r="D66" t="n">
+        <v>0.04541983418685399</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.03572871841071963</v>
       </c>
     </row>
     <row r="67">
@@ -2184,13 +2062,11 @@
       <c r="C67" t="n">
         <v>136.76</v>
       </c>
-      <c r="D67">
-        <f>LN(B67/B66)</f>
-        <v/>
-      </c>
-      <c r="E67">
-        <f>LN(C67/C66)</f>
-        <v/>
+      <c r="D67" t="n">
+        <v>0.01227376351812045</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.01021579457340559</v>
       </c>
     </row>
     <row r="68">
@@ -2203,13 +2079,11 @@
       <c r="C68" t="n">
         <v>135.37</v>
       </c>
-      <c r="D68">
-        <f>LN(B68/B67)</f>
-        <v/>
-      </c>
-      <c r="E68">
-        <f>LN(C68/C67)</f>
-        <v/>
+      <c r="D68" t="n">
+        <v>-0.007172091333684891</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.04147782007569599</v>
       </c>
     </row>
     <row r="69">
@@ -2222,13 +2096,11 @@
       <c r="C69" t="n">
         <v>129.87</v>
       </c>
-      <c r="D69">
-        <f>LN(B69/B68)</f>
-        <v/>
-      </c>
-      <c r="E69">
-        <f>LN(C69/C68)</f>
-        <v/>
+      <c r="D69" t="n">
+        <v>-0.02476460670416382</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.06859694947841428</v>
       </c>
     </row>
     <row r="70">
@@ -2241,13 +2113,11 @@
       <c r="C70" t="n">
         <v>121.26</v>
       </c>
-      <c r="D70">
-        <f>LN(B70/B69)</f>
-        <v/>
-      </c>
-      <c r="E70">
-        <f>LN(C70/C69)</f>
-        <v/>
+      <c r="D70" t="n">
+        <v>0.008046466492958593</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.001318609058703353</v>
       </c>
     </row>
     <row r="71">
@@ -2260,13 +2130,11 @@
       <c r="C71" t="n">
         <v>121.42</v>
       </c>
-      <c r="D71">
-        <f>LN(B71/B70)</f>
-        <v/>
-      </c>
-      <c r="E71">
-        <f>LN(C71/C70)</f>
-        <v/>
+      <c r="D71" t="n">
+        <v>0.02605063257962707</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.003217160951775575</v>
       </c>
     </row>
     <row r="72">
@@ -2279,13 +2147,11 @@
       <c r="C72" t="n">
         <v>121.03</v>
       </c>
-      <c r="D72">
-        <f>LN(B72/B71)</f>
-        <v/>
-      </c>
-      <c r="E72">
-        <f>LN(C72/C71)</f>
-        <v/>
+      <c r="D72" t="n">
+        <v>-0.007698181196592032</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.008630042774214928</v>
       </c>
     </row>
     <row r="73">
@@ -2298,13 +2164,11 @@
       <c r="C73" t="n">
         <v>119.99</v>
       </c>
-      <c r="D73">
-        <f>LN(B73/B72)</f>
-        <v/>
-      </c>
-      <c r="E73">
-        <f>LN(C73/C72)</f>
-        <v/>
+      <c r="D73" t="n">
+        <v>0.01557911939816088</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.01011617250612305</v>
       </c>
     </row>
     <row r="74">
@@ -2317,13 +2181,11 @@
       <c r="C74" t="n">
         <v>121.21</v>
       </c>
-      <c r="D74">
-        <f>LN(B74/B73)</f>
-        <v/>
-      </c>
-      <c r="E74">
-        <f>LN(C74/C73)</f>
-        <v/>
+      <c r="D74" t="n">
+        <v>0.011340545660177</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.01465977688999683</v>
       </c>
     </row>
     <row r="75">
@@ -2336,13 +2198,11 @@
       <c r="C75" t="n">
         <v>123</v>
       </c>
-      <c r="D75">
-        <f>LN(B75/B74)</f>
-        <v/>
-      </c>
-      <c r="E75">
-        <f>LN(C75/C74)</f>
-        <v/>
+      <c r="D75" t="n">
+        <v>0.02673724405280272</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.07808958205265443</v>
       </c>
     </row>
     <row r="76">
@@ -2355,13 +2215,11 @@
       <c r="C76" t="n">
         <v>132.99</v>
       </c>
-      <c r="D76">
-        <f>LN(B76/B75)</f>
-        <v/>
-      </c>
-      <c r="E76">
-        <f>LN(C76/C75)</f>
-        <v/>
+      <c r="D76" t="n">
+        <v>0.01363219563746931</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.008759180089881554</v>
       </c>
     </row>
     <row r="77">
@@ -2374,13 +2232,11 @@
       <c r="C77" t="n">
         <v>134.16</v>
       </c>
-      <c r="D77">
-        <f>LN(B77/B76)</f>
-        <v/>
-      </c>
-      <c r="E77">
-        <f>LN(C77/C76)</f>
-        <v/>
+      <c r="D77" t="n">
+        <v>-0.001267087923721601</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.001191895254331903</v>
       </c>
     </row>
     <row r="78">
@@ -2393,13 +2249,11 @@
       <c r="C78" t="n">
         <v>134.32</v>
       </c>
-      <c r="D78">
-        <f>LN(B78/B77)</f>
-        <v/>
-      </c>
-      <c r="E78">
-        <f>LN(C78/C77)</f>
-        <v/>
+      <c r="D78" t="n">
+        <v>0.0002391961108548356</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.02152238993385512</v>
       </c>
     </row>
     <row r="79">
@@ -2412,13 +2266,11 @@
       <c r="C79" t="n">
         <v>131.46</v>
       </c>
-      <c r="D79">
-        <f>LN(B79/B78)</f>
-        <v/>
-      </c>
-      <c r="E79">
-        <f>LN(C79/C78)</f>
-        <v/>
+      <c r="D79" t="n">
+        <v>0.01222534976723322</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.009554091094793212</v>
       </c>
     </row>
     <row r="80">
@@ -2431,13 +2283,11 @@
       <c r="C80" t="n">
         <v>130.21</v>
       </c>
-      <c r="D80">
-        <f>LN(B80/B79)</f>
-        <v/>
-      </c>
-      <c r="E80">
-        <f>LN(C80/C79)</f>
-        <v/>
+      <c r="D80" t="n">
+        <v>-0.01397759018626544</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.02142440091851256</v>
       </c>
     </row>
     <row r="81">
@@ -2450,13 +2300,11 @@
       <c r="C81" t="n">
         <v>127.45</v>
       </c>
-      <c r="D81">
-        <f>LN(B81/B80)</f>
-        <v/>
-      </c>
-      <c r="E81">
-        <f>LN(C81/C80)</f>
-        <v/>
+      <c r="D81" t="n">
+        <v>-0.004319484825130171</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-0.01597629678554109</v>
       </c>
     </row>
     <row r="82">
@@ -2469,13 +2317,11 @@
       <c r="C82" t="n">
         <v>125.43</v>
       </c>
-      <c r="D82">
-        <f>LN(B82/B81)</f>
-        <v/>
-      </c>
-      <c r="E82">
-        <f>LN(C82/C81)</f>
-        <v/>
+      <c r="D82" t="n">
+        <v>0.01154323179618438</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.006558974081807237</v>
       </c>
     </row>
     <row r="83">
@@ -2488,13 +2334,11 @@
       <c r="C83" t="n">
         <v>124.61</v>
       </c>
-      <c r="D83">
-        <f>LN(B83/B82)</f>
-        <v/>
-      </c>
-      <c r="E83">
-        <f>LN(C83/C82)</f>
-        <v/>
+      <c r="D83" t="n">
+        <v>0.006113369762920371</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.0102196498233918</v>
       </c>
     </row>
     <row r="84">
@@ -2507,13 +2351,11 @@
       <c r="C84" t="n">
         <v>125.89</v>
       </c>
-      <c r="D84">
-        <f>LN(B84/B83)</f>
-        <v/>
-      </c>
-      <c r="E84">
-        <f>LN(C84/C83)</f>
-        <v/>
+      <c r="D84" t="n">
+        <v>0.004140460515807119</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.01153069164729811</v>
       </c>
     </row>
     <row r="85">
@@ -2526,13 +2368,11 @@
       <c r="C85" t="n">
         <v>127.35</v>
       </c>
-      <c r="D85">
-        <f>LN(B85/B84)</f>
-        <v/>
-      </c>
-      <c r="E85">
-        <f>LN(C85/C84)</f>
-        <v/>
+      <c r="D85" t="n">
+        <v>-0.01925209421963388</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.02412746494248406</v>
       </c>
     </row>
     <row r="86">
@@ -2545,13 +2385,11 @@
       <c r="C86" t="n">
         <v>130.46</v>
       </c>
-      <c r="D86">
-        <f>LN(B86/B85)</f>
-        <v/>
-      </c>
-      <c r="E86">
-        <f>LN(C86/C85)</f>
-        <v/>
+      <c r="D86" t="n">
+        <v>0.02705219333440339</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.02010918769097787</v>
       </c>
     </row>
     <row r="87">
@@ -2564,13 +2402,11 @@
       <c r="C87" t="n">
         <v>133.11</v>
       </c>
-      <c r="D87">
-        <f>LN(B87/B86)</f>
-        <v/>
-      </c>
-      <c r="E87">
-        <f>LN(C87/C86)</f>
-        <v/>
+      <c r="D87" t="n">
+        <v>0.01659708387954048</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.05018081344055934</v>
       </c>
     </row>
     <row r="88">
@@ -2583,13 +2419,11 @@
       <c r="C88" t="n">
         <v>139.96</v>
       </c>
-      <c r="D88">
-        <f>LN(B88/B87)</f>
-        <v/>
-      </c>
-      <c r="E88">
-        <f>LN(C88/C87)</f>
-        <v/>
+      <c r="D88" t="n">
+        <v>0.003946397474809342</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.03613540800351425</v>
       </c>
     </row>
     <row r="89">
@@ -2602,13 +2436,11 @@
       <c r="C89" t="n">
         <v>145.11</v>
       </c>
-      <c r="D89">
-        <f>LN(B89/B88)</f>
-        <v/>
-      </c>
-      <c r="E89">
-        <f>LN(C89/C88)</f>
-        <v/>
+      <c r="D89" t="n">
+        <v>-0.0097485912973343</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.008782217680318796</v>
       </c>
     </row>
     <row r="90">
@@ -2621,13 +2453,11 @@
       <c r="C90" t="n">
         <v>146.39</v>
       </c>
-      <c r="D90">
-        <f>LN(B90/B89)</f>
-        <v/>
-      </c>
-      <c r="E90">
-        <f>LN(C90/C89)</f>
-        <v/>
+      <c r="D90" t="n">
+        <v>0.01936906511747471</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.01471462386113007</v>
       </c>
     </row>
     <row r="91">
@@ -2640,13 +2470,11 @@
       <c r="C91" t="n">
         <v>148.56</v>
       </c>
-      <c r="D91">
-        <f>LN(B91/B90)</f>
-        <v/>
-      </c>
-      <c r="E91">
-        <f>LN(C91/C90)</f>
-        <v/>
+      <c r="D91" t="n">
+        <v>-0.003753815275381728</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-0.0183416594883633</v>
       </c>
     </row>
     <row r="92">
@@ -2659,13 +2487,11 @@
       <c r="C92" t="n">
         <v>145.86</v>
       </c>
-      <c r="D92">
-        <f>LN(B92/B91)</f>
-        <v/>
-      </c>
-      <c r="E92">
-        <f>LN(C92/C91)</f>
-        <v/>
+      <c r="D92" t="n">
+        <v>0.009343597819637867</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.001917808806984558</v>
       </c>
     </row>
     <row r="93">
@@ -2678,13 +2504,11 @@
       <c r="C93" t="n">
         <v>146.14</v>
       </c>
-      <c r="D93">
-        <f>LN(B93/B92)</f>
-        <v/>
-      </c>
-      <c r="E93">
-        <f>LN(C93/C92)</f>
-        <v/>
+      <c r="D93" t="n">
+        <v>0.00707059586570617</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.02005215540762109</v>
       </c>
     </row>
     <row r="94">
@@ -2697,13 +2521,11 @@
       <c r="C94" t="n">
         <v>149.1</v>
       </c>
-      <c r="D94">
-        <f>LN(B94/B93)</f>
-        <v/>
-      </c>
-      <c r="E94">
-        <f>LN(C94/C93)</f>
-        <v/>
+      <c r="D94" t="n">
+        <v>-0.005910449354394162</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-0.006121987568605595</v>
       </c>
     </row>
     <row r="95">
@@ -2716,13 +2538,11 @@
       <c r="C95" t="n">
         <v>148.19</v>
       </c>
-      <c r="D95">
-        <f>LN(B95/B94)</f>
-        <v/>
-      </c>
-      <c r="E95">
-        <f>LN(C95/C94)</f>
-        <v/>
+      <c r="D95" t="n">
+        <v>0.01512702232581491</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.002762898081571725</v>
       </c>
     </row>
     <row r="96">
@@ -2735,13 +2555,11 @@
       <c r="C96" t="n">
         <v>148.6</v>
       </c>
-      <c r="D96">
-        <f>LN(B96/B95)</f>
-        <v/>
-      </c>
-      <c r="E96">
-        <f>LN(C96/C95)</f>
-        <v/>
+      <c r="D96" t="n">
+        <v>0.005762442975362384</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.03764062708545651</v>
       </c>
     </row>
     <row r="97">
@@ -2754,13 +2572,11 @@
       <c r="C97" t="n">
         <v>154.3</v>
       </c>
-      <c r="D97">
-        <f>LN(B97/B96)</f>
-        <v/>
-      </c>
-      <c r="E97">
-        <f>LN(C97/C96)</f>
-        <v/>
+      <c r="D97" t="n">
+        <v>-0.01708956746746089</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-0.03515381597761371</v>
       </c>
     </row>
     <row r="98">
@@ -2773,13 +2589,11 @@
       <c r="C98" t="n">
         <v>148.97</v>
       </c>
-      <c r="D98">
-        <f>LN(B98/B97)</f>
-        <v/>
-      </c>
-      <c r="E98">
-        <f>LN(C98/C97)</f>
-        <v/>
+      <c r="D98" t="n">
+        <v>-0.00575602973461195</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-0.01972744719953786</v>
       </c>
     </row>
     <row r="99">
@@ -2792,13 +2606,11 @@
       <c r="C99" t="n">
         <v>146.06</v>
       </c>
-      <c r="D99">
-        <f>LN(B99/B98)</f>
-        <v/>
-      </c>
-      <c r="E99">
-        <f>LN(C99/C98)</f>
-        <v/>
+      <c r="D99" t="n">
+        <v>0.005060499274872533</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.005870724759502686</v>
       </c>
     </row>
     <row r="100">
@@ -2811,13 +2623,11 @@
       <c r="C100" t="n">
         <v>146.92</v>
       </c>
-      <c r="D100">
-        <f>LN(B100/B99)</f>
-        <v/>
-      </c>
-      <c r="E100">
-        <f>LN(C100/C99)</f>
-        <v/>
+      <c r="D100" t="n">
+        <v>-0.02234187150450074</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-0.02949414329195749</v>
       </c>
     </row>
     <row r="101">
@@ -2830,13 +2640,11 @@
       <c r="C101" t="n">
         <v>142.65</v>
       </c>
-      <c r="D101">
-        <f>LN(B101/B100)</f>
-        <v/>
-      </c>
-      <c r="E101">
-        <f>LN(C101/C100)</f>
-        <v/>
+      <c r="D101" t="n">
+        <v>0.007841491968997224</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.001751007276312782</v>
       </c>
     </row>
     <row r="102">
@@ -2849,13 +2657,11 @@
       <c r="C102" t="n">
         <v>142.9</v>
       </c>
-      <c r="D102">
-        <f>LN(B102/B101)</f>
-        <v/>
-      </c>
-      <c r="E102">
-        <f>LN(C102/C101)</f>
-        <v/>
+      <c r="D102" t="n">
+        <v>0.01806042967243386</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.0134845999616187</v>
       </c>
     </row>
     <row r="103">
@@ -2868,13 +2674,11 @@
       <c r="C103" t="n">
         <v>144.84</v>
       </c>
-      <c r="D103">
-        <f>LN(B103/B102)</f>
-        <v/>
-      </c>
-      <c r="E103">
-        <f>LN(C103/C102)</f>
-        <v/>
+      <c r="D103" t="n">
+        <v>0.01631087582370259</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.0262339168116914</v>
       </c>
     </row>
     <row r="104">
@@ -2887,13 +2691,11 @@
       <c r="C104" t="n">
         <v>148.69</v>
       </c>
-      <c r="D104">
-        <f>LN(B104/B103)</f>
-        <v/>
-      </c>
-      <c r="E104">
-        <f>LN(C104/C103)</f>
-        <v/>
+      <c r="D104" t="n">
+        <v>0.01321946011668036</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.007437469373987412</v>
       </c>
     </row>
     <row r="105">
@@ -2906,13 +2708,11 @@
       <c r="C105" t="n">
         <v>149.8</v>
       </c>
-      <c r="D105">
-        <f>LN(B105/B104)</f>
-        <v/>
-      </c>
-      <c r="E105">
-        <f>LN(C105/C104)</f>
-        <v/>
+      <c r="D105" t="n">
+        <v>0.0198116533569717</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.009831353267082848</v>
       </c>
     </row>
     <row r="106">
@@ -2925,13 +2725,11 @@
       <c r="C106" t="n">
         <v>151.28</v>
       </c>
-      <c r="D106">
-        <f>LN(B106/B105)</f>
-        <v/>
-      </c>
-      <c r="E106">
-        <f>LN(C106/C105)</f>
-        <v/>
+      <c r="D106" t="n">
+        <v>-0.00312993972193239</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-0.008563799142933958</v>
       </c>
     </row>
     <row r="107">
@@ -2944,13 +2742,11 @@
       <c r="C107" t="n">
         <v>149.99</v>
       </c>
-      <c r="D107">
-        <f>LN(B107/B106)</f>
-        <v/>
-      </c>
-      <c r="E107">
-        <f>LN(C107/C106)</f>
-        <v/>
+      <c r="D107" t="n">
+        <v>0.003221473000196812</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.0680367953282548</v>
       </c>
     </row>
     <row r="108">
@@ -2963,13 +2759,11 @@
       <c r="C108" t="n">
         <v>160.55</v>
       </c>
-      <c r="D108">
-        <f>LN(B108/B107)</f>
-        <v/>
-      </c>
-      <c r="E108">
-        <f>LN(C108/C107)</f>
-        <v/>
+      <c r="D108" t="n">
+        <v>-0.02224231813657183</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-0.02357053914258281</v>
       </c>
     </row>
     <row r="109">
@@ -2982,13 +2776,11 @@
       <c r="C109" t="n">
         <v>156.81</v>
       </c>
-      <c r="D109">
-        <f>LN(B109/B108)</f>
-        <v/>
-      </c>
-      <c r="E109">
-        <f>LN(C109/C108)</f>
-        <v/>
+      <c r="D109" t="n">
+        <v>-0.01230491653501995</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.03157331146654982</v>
       </c>
     </row>
     <row r="110">
@@ -3001,13 +2793,11 @@
       <c r="C110" t="n">
         <v>161.84</v>
       </c>
-      <c r="D110">
-        <f>LN(B110/B109)</f>
-        <v/>
-      </c>
-      <c r="E110">
-        <f>LN(C110/C109)</f>
-        <v/>
+      <c r="D110" t="n">
+        <v>0.03753555355495608</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.1032884247341262</v>
       </c>
     </row>
     <row r="111">
@@ -3020,13 +2810,11 @@
       <c r="C111" t="n">
         <v>179.45</v>
       </c>
-      <c r="D111">
-        <f>LN(B111/B110)</f>
-        <v/>
-      </c>
-      <c r="E111">
-        <f>LN(C111/C110)</f>
-        <v/>
+      <c r="D111" t="n">
+        <v>-0.01958346718441198</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-0.04741468260370758</v>
       </c>
     </row>
     <row r="112">
@@ -3039,13 +2827,11 @@
       <c r="C112" t="n">
         <v>171.14</v>
       </c>
-      <c r="D112">
-        <f>LN(B112/B111)</f>
-        <v/>
-      </c>
-      <c r="E112">
-        <f>LN(C112/C111)</f>
-        <v/>
+      <c r="D112" t="n">
+        <v>0.02250151909920825</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.02959170498387753</v>
       </c>
     </row>
     <row r="113">
@@ -3058,13 +2844,11 @@
       <c r="C113" t="n">
         <v>176.28</v>
       </c>
-      <c r="D113">
-        <f>LN(B113/B112)</f>
-        <v/>
-      </c>
-      <c r="E113">
-        <f>LN(C113/C112)</f>
-        <v/>
+      <c r="D113" t="n">
+        <v>0.008510402746061253</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.007291257396957003</v>
       </c>
     </row>
     <row r="114">
@@ -3077,13 +2861,11 @@
       <c r="C114" t="n">
         <v>177.57</v>
       </c>
-      <c r="D114">
-        <f>LN(B114/B113)</f>
-        <v/>
-      </c>
-      <c r="E114">
-        <f>LN(C114/C113)</f>
-        <v/>
+      <c r="D114" t="n">
+        <v>-0.01888185239194662</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-0.03088253658236251</v>
       </c>
     </row>
     <row r="115">
@@ -3096,13 +2878,11 @@
       <c r="C115" t="n">
         <v>172.17</v>
       </c>
-      <c r="D115">
-        <f>LN(B115/B114)</f>
-        <v/>
-      </c>
-      <c r="E115">
-        <f>LN(C115/C114)</f>
-        <v/>
+      <c r="D115" t="n">
+        <v>-0.003036443914687181</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.005213776148526796</v>
       </c>
     </row>
     <row r="116">
@@ -3115,13 +2895,11 @@
       <c r="C116" t="n">
         <v>173.07</v>
       </c>
-      <c r="D116">
-        <f>LN(B116/B115)</f>
-        <v/>
-      </c>
-      <c r="E116">
-        <f>LN(C116/C115)</f>
-        <v/>
+      <c r="D116" t="n">
+        <v>-0.05849059970196813</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-0.06357213475039621</v>
       </c>
     </row>
     <row r="117">
@@ -3134,13 +2912,11 @@
       <c r="C117" t="n">
         <v>162.41</v>
       </c>
-      <c r="D117">
-        <f>LN(B117/B116)</f>
-        <v/>
-      </c>
-      <c r="E117">
-        <f>LN(C117/C116)</f>
-        <v/>
+      <c r="D117" t="n">
+        <v>0.007680854632186251</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.04761372968597441</v>
       </c>
     </row>
     <row r="118">
@@ -3153,13 +2929,11 @@
       <c r="C118" t="n">
         <v>170.33</v>
       </c>
-      <c r="D118">
-        <f>LN(B118/B117)</f>
-        <v/>
-      </c>
-      <c r="E118">
-        <f>LN(C118/C117)</f>
-        <v/>
+      <c r="D118" t="n">
+        <v>0.01537806351190111</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.01202162003440122</v>
       </c>
     </row>
     <row r="119">
@@ -3172,13 +2946,11 @@
       <c r="C119" t="n">
         <v>172.39</v>
       </c>
-      <c r="D119">
-        <f>LN(B119/B118)</f>
-        <v/>
-      </c>
-      <c r="E119">
-        <f>LN(C119/C118)</f>
-        <v/>
+      <c r="D119" t="n">
+        <v>-0.01836321118386986</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.02199308655388982</v>
       </c>
     </row>
     <row r="120">
@@ -3191,13 +2963,11 @@
       <c r="C120" t="n">
         <v>168.64</v>
       </c>
-      <c r="D120">
-        <f>LN(B120/B119)</f>
-        <v/>
-      </c>
-      <c r="E120">
-        <f>LN(C120/C119)</f>
-        <v/>
+      <c r="D120" t="n">
+        <v>-0.01591591519537441</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.007977657360219095</v>
       </c>
     </row>
     <row r="121">
@@ -3210,13 +2980,11 @@
       <c r="C121" t="n">
         <v>167.3</v>
       </c>
-      <c r="D121">
-        <f>LN(B121/B120)</f>
-        <v/>
-      </c>
-      <c r="E121">
-        <f>LN(C121/C120)</f>
-        <v/>
+      <c r="D121" t="n">
+        <v>0.008193763839142623</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.0147526384750383</v>
       </c>
     </row>
     <row r="122">
@@ -3229,13 +2997,11 @@
       <c r="C122" t="n">
         <v>164.85</v>
       </c>
-      <c r="D122">
-        <f>LN(B122/B121)</f>
-        <v/>
-      </c>
-      <c r="E122">
-        <f>LN(C122/C121)</f>
-        <v/>
+      <c r="D122" t="n">
+        <v>-0.01280326709978914</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01024336741476099</v>
       </c>
     </row>
     <row r="123">
@@ -3248,13 +3014,11 @@
       <c r="C123" t="n">
         <v>163.17</v>
       </c>
-      <c r="D123">
-        <f>LN(B123/B122)</f>
-        <v/>
-      </c>
-      <c r="E123">
-        <f>LN(C123/C122)</f>
-        <v/>
+      <c r="D123" t="n">
+        <v>-0.02919634838689788</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-0.05311093960139774</v>
       </c>
     </row>
     <row r="124">
@@ -3267,13 +3031,11 @@
       <c r="C124" t="n">
         <v>154.73</v>
       </c>
-      <c r="D124">
-        <f>LN(B124/B123)</f>
-        <v/>
-      </c>
-      <c r="E124">
-        <f>LN(C124/C123)</f>
-        <v/>
+      <c r="D124" t="n">
+        <v>0.05973788343732887</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.05806280666645039</v>
       </c>
     </row>
     <row r="125">
@@ -3286,13 +3048,11 @@
       <c r="C125" t="n">
         <v>163.98</v>
       </c>
-      <c r="D125">
-        <f>LN(B125/B124)</f>
-        <v/>
-      </c>
-      <c r="E125">
-        <f>LN(C125/C124)</f>
-        <v/>
+      <c r="D125" t="n">
+        <v>0.01775272079257011</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.06344022338850873</v>
       </c>
     </row>
     <row r="126">
@@ -3305,13 +3065,11 @@
       <c r="C126" t="n">
         <v>174.72</v>
       </c>
-      <c r="D126">
-        <f>LN(B126/B125)</f>
-        <v/>
-      </c>
-      <c r="E126">
-        <f>LN(C126/C125)</f>
-        <v/>
+      <c r="D126" t="n">
+        <v>0.0006161348297878712</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.002349369329766075</v>
       </c>
     </row>
     <row r="127">
@@ -3324,13 +3082,11 @@
       <c r="C127" t="n">
         <v>174.31</v>
       </c>
-      <c r="D127">
-        <f>LN(B127/B126)</f>
-        <v/>
-      </c>
-      <c r="E127">
-        <f>LN(C127/C126)</f>
-        <v/>
+      <c r="D127" t="n">
+        <v>-0.01274737378558377</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.0245076145007737</v>
       </c>
     </row>
     <row r="128">
@@ -3343,13 +3099,11 @@
       <c r="C128" t="n">
         <v>170.09</v>
       </c>
-      <c r="D128">
-        <f>LN(B128/B127)</f>
-        <v/>
-      </c>
-      <c r="E128">
-        <f>LN(C128/C127)</f>
-        <v/>
+      <c r="D128" t="n">
+        <v>-0.02155052452621062</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.02862620179673835</v>
       </c>
     </row>
     <row r="129">
@@ -3362,13 +3116,11 @@
       <c r="C129" t="n">
         <v>165.29</v>
       </c>
-      <c r="D129">
-        <f>LN(B129/B128)</f>
-        <v/>
-      </c>
-      <c r="E129">
-        <f>LN(C129/C128)</f>
-        <v/>
+      <c r="D129" t="n">
+        <v>-0.02788842813541886</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-0.02140230891201668</v>
       </c>
     </row>
     <row r="130">
@@ -3381,13 +3133,11 @@
       <c r="C130" t="n">
         <v>161.79</v>
       </c>
-      <c r="D130">
-        <f>LN(B130/B129)</f>
-        <v/>
-      </c>
-      <c r="E130">
-        <f>LN(C130/C129)</f>
-        <v/>
+      <c r="D130" t="n">
+        <v>-0.03328599203927917</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.02592181202617541</v>
       </c>
     </row>
     <row r="131">
@@ -3400,13 +3150,11 @@
       <c r="C131" t="n">
         <v>157.65</v>
       </c>
-      <c r="D131">
-        <f>LN(B131/B130)</f>
-        <v/>
-      </c>
-      <c r="E131">
-        <f>LN(C131/C130)</f>
-        <v/>
+      <c r="D131" t="n">
+        <v>-0.002081095615345063</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-0.002349729592213406</v>
       </c>
     </row>
     <row r="132">
@@ -3419,13 +3167,11 @@
       <c r="C132" t="n">
         <v>157.28</v>
       </c>
-      <c r="D132">
-        <f>LN(B132/B131)</f>
-        <v/>
-      </c>
-      <c r="E132">
-        <f>LN(C132/C131)</f>
-        <v/>
+      <c r="D132" t="n">
+        <v>-0.02441441811014675</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-0.06684705013673588</v>
       </c>
     </row>
     <row r="133">
@@ -3438,13 +3184,11 @@
       <c r="C133" t="n">
         <v>147.11</v>
       </c>
-      <c r="D133">
-        <f>LN(B133/B132)</f>
-        <v/>
-      </c>
-      <c r="E133">
-        <f>LN(C133/C132)</f>
-        <v/>
+      <c r="D133" t="n">
+        <v>-0.03092388614336145</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-0.06690235782239534</v>
       </c>
     </row>
     <row r="134">
@@ -3457,13 +3201,11 @@
       <c r="C134" t="n">
         <v>137.59</v>
       </c>
-      <c r="D134">
-        <f>LN(B134/B133)</f>
-        <v/>
-      </c>
-      <c r="E134">
-        <f>LN(C134/C133)</f>
-        <v/>
+      <c r="D134" t="n">
+        <v>0.06376669753145632</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.08395416104022017</v>
       </c>
     </row>
     <row r="135">
@@ -3476,13 +3218,11 @@
       <c r="C135" t="n">
         <v>149.64</v>
       </c>
-      <c r="D135">
-        <f>LN(B135/B134)</f>
-        <v/>
-      </c>
-      <c r="E135">
-        <f>LN(C135/C134)</f>
-        <v/>
+      <c r="D135" t="n">
+        <v>-0.01202417357274058</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.02888140542345598</v>
       </c>
     </row>
     <row r="136">
@@ -3495,13 +3235,11 @@
       <c r="C136" t="n">
         <v>145.38</v>
       </c>
-      <c r="D136">
-        <f>LN(B136/B135)</f>
-        <v/>
-      </c>
-      <c r="E136">
-        <f>LN(C136/C135)</f>
-        <v/>
+      <c r="D136" t="n">
+        <v>-0.05187069260832693</v>
+      </c>
+      <c r="E136" t="n">
+        <v>-0.05842162304472673</v>
       </c>
     </row>
     <row r="137">
@@ -3514,13 +3252,11 @@
       <c r="C137" t="n">
         <v>137.13</v>
       </c>
-      <c r="D137">
-        <f>LN(B137/B136)</f>
-        <v/>
-      </c>
-      <c r="E137">
-        <f>LN(C137/C136)</f>
-        <v/>
+      <c r="D137" t="n">
+        <v>-0.05968744734468188</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04146635969090637</v>
       </c>
     </row>
     <row r="138">
@@ -3533,13 +3269,11 @@
       <c r="C138" t="n">
         <v>131.56</v>
       </c>
-      <c r="D138">
-        <f>LN(B138/B137)</f>
-        <v/>
-      </c>
-      <c r="E138">
-        <f>LN(C138/C137)</f>
-        <v/>
+      <c r="D138" t="n">
+        <v>0.06247269349412064</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.07396679900462023</v>
       </c>
     </row>
     <row r="139">
@@ -3552,13 +3286,11 @@
       <c r="C139" t="n">
         <v>141.66</v>
       </c>
-      <c r="D139">
-        <f>LN(B139/B138)</f>
-        <v/>
-      </c>
-      <c r="E139">
-        <f>LN(C139/C138)</f>
-        <v/>
+      <c r="D139" t="n">
+        <v>-0.02233754972930236</v>
+      </c>
+      <c r="E139" t="n">
+        <v>-0.01945961116470618</v>
       </c>
     </row>
     <row r="140">
@@ -3571,13 +3303,11 @@
       <c r="C140" t="n">
         <v>138.93</v>
       </c>
-      <c r="D140">
-        <f>LN(B140/B139)</f>
-        <v/>
-      </c>
-      <c r="E140">
-        <f>LN(C140/C139)</f>
-        <v/>
+      <c r="D140" t="n">
+        <v>0.01917282807199193</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.05673444944660645</v>
       </c>
     </row>
     <row r="141">
@@ -3590,13 +3320,11 @@
       <c r="C141" t="n">
         <v>147.04</v>
       </c>
-      <c r="D141">
-        <f>LN(B141/B140)</f>
-        <v/>
-      </c>
-      <c r="E141">
-        <f>LN(C141/C140)</f>
-        <v/>
+      <c r="D141" t="n">
+        <v>-0.009332064725854666</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.0210633270848125</v>
       </c>
     </row>
     <row r="142">
@@ -3609,13 +3337,11 @@
       <c r="C142" t="n">
         <v>150.17</v>
       </c>
-      <c r="D142">
-        <f>LN(B142/B141)</f>
-        <v/>
-      </c>
-      <c r="E142">
-        <f>LN(C142/C141)</f>
-        <v/>
+      <c r="D142" t="n">
+        <v>0.02517005532430331</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.0257688616015728</v>
       </c>
     </row>
     <row r="143">
@@ -3628,13 +3354,11 @@
       <c r="C143" t="n">
         <v>154.09</v>
       </c>
-      <c r="D143">
-        <f>LN(B143/B142)</f>
-        <v/>
-      </c>
-      <c r="E143">
-        <f>LN(C143/C142)</f>
-        <v/>
+      <c r="D143" t="n">
+        <v>0.04169206568814191</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.05320269104415506</v>
       </c>
     </row>
     <row r="144">
@@ -3647,13 +3371,11 @@
       <c r="C144" t="n">
         <v>162.51</v>
       </c>
-      <c r="D144">
-        <f>LN(B144/B143)</f>
-        <v/>
-      </c>
-      <c r="E144">
-        <f>LN(C144/C143)</f>
-        <v/>
+      <c r="D144" t="n">
+        <v>0.003601003470727537</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.01732490108988469</v>
       </c>
     </row>
     <row r="145">
@@ -3666,13 +3388,11 @@
       <c r="C145" t="n">
         <v>165.35</v>
       </c>
-      <c r="D145">
-        <f>LN(B145/B144)</f>
-        <v/>
-      </c>
-      <c r="E145">
-        <f>LN(C145/C144)</f>
-        <v/>
+      <c r="D145" t="n">
+        <v>0.03203942981237315</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.04001126378969195</v>
       </c>
     </row>
     <row r="146">
@@ -3685,13 +3405,11 @@
       <c r="C146" t="n">
         <v>172.1</v>
       </c>
-      <c r="D146">
-        <f>LN(B146/B145)</f>
-        <v/>
-      </c>
-      <c r="E146">
-        <f>LN(C146/C145)</f>
-        <v/>
+      <c r="D146" t="n">
+        <v>-0.01214546528922597</v>
+      </c>
+      <c r="E146" t="n">
+        <v>-0.003375825335056465</v>
       </c>
     </row>
     <row r="147">
@@ -3704,13 +3422,11 @@
       <c r="C147" t="n">
         <v>171.52</v>
       </c>
-      <c r="D147">
-        <f>LN(B147/B146)</f>
-        <v/>
-      </c>
-      <c r="E147">
-        <f>LN(C147/C146)</f>
-        <v/>
+      <c r="D147" t="n">
+        <v>-0.04123613764169557</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-0.04715321179688502</v>
       </c>
     </row>
     <row r="148">
@@ -3723,13 +3439,11 @@
       <c r="C148" t="n">
         <v>163.62</v>
       </c>
-      <c r="D148">
-        <f>LN(B148/B147)</f>
-        <v/>
-      </c>
-      <c r="E148">
-        <f>LN(C148/C147)</f>
-        <v/>
+      <c r="D148" t="n">
+        <v>-0.03342865435007206</v>
+      </c>
+      <c r="E148" t="n">
+        <v>-0.04890934985628896</v>
       </c>
     </row>
     <row r="149">
@@ -3742,13 +3456,11 @@
       <c r="C149" t="n">
         <v>155.81</v>
       </c>
-      <c r="D149">
-        <f>LN(B149/B148)</f>
-        <v/>
-      </c>
-      <c r="E149">
-        <f>LN(C149/C148)</f>
-        <v/>
+      <c r="D149" t="n">
+        <v>0.03581634191474267</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.009962404383509713</v>
       </c>
     </row>
     <row r="150">
@@ -3761,13 +3473,11 @@
       <c r="C150" t="n">
         <v>157.37</v>
       </c>
-      <c r="D150">
-        <f>LN(B150/B149)</f>
-        <v/>
-      </c>
-      <c r="E150">
-        <f>LN(C150/C149)</f>
-        <v/>
+      <c r="D150" t="n">
+        <v>-0.04887953817221694</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-0.04330861498032337</v>
       </c>
     </row>
     <row r="151">
@@ -3780,13 +3490,11 @@
       <c r="C151" t="n">
         <v>150.7</v>
       </c>
-      <c r="D151">
-        <f>LN(B151/B150)</f>
-        <v/>
-      </c>
-      <c r="E151">
-        <f>LN(C151/C150)</f>
-        <v/>
+      <c r="D151" t="n">
+        <v>-0.04761318824981041</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-0.001793245922717225</v>
       </c>
     </row>
     <row r="152">
@@ -3799,13 +3507,11 @@
       <c r="C152" t="n">
         <v>150.43</v>
       </c>
-      <c r="D152">
-        <f>LN(B152/B151)</f>
-        <v/>
-      </c>
-      <c r="E152">
-        <f>LN(C152/C151)</f>
-        <v/>
+      <c r="D152" t="n">
+        <v>-0.02957001200428394</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-0.084795948376163</v>
       </c>
     </row>
     <row r="153">
@@ -3818,13 +3524,11 @@
       <c r="C153" t="n">
         <v>138.2</v>
       </c>
-      <c r="D153">
-        <f>LN(B153/B152)</f>
-        <v/>
-      </c>
-      <c r="E153">
-        <f>LN(C153/C152)</f>
-        <v/>
+      <c r="D153" t="n">
+        <v>0.0149588687765822</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.01358316187445316</v>
       </c>
     </row>
     <row r="154">
@@ -3837,13 +3541,11 @@
       <c r="C154" t="n">
         <v>140.09</v>
       </c>
-      <c r="D154">
-        <f>LN(B154/B153)</f>
-        <v/>
-      </c>
-      <c r="E154">
-        <f>LN(C154/C153)</f>
-        <v/>
+      <c r="D154" t="n">
+        <v>-0.01567029585950877</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-0.01228154913735764</v>
       </c>
     </row>
     <row r="155">
@@ -3856,13 +3558,11 @@
       <c r="C155" t="n">
         <v>138.38</v>
       </c>
-      <c r="D155">
-        <f>LN(B155/B154)</f>
-        <v/>
-      </c>
-      <c r="E155">
-        <f>LN(C155/C154)</f>
-        <v/>
+      <c r="D155" t="n">
+        <v>0.04626892972508202</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.06226411266740595</v>
       </c>
     </row>
     <row r="156">
@@ -3875,13 +3575,11 @@
       <c r="C156" t="n">
         <v>147.27</v>
       </c>
-      <c r="D156">
-        <f>LN(B156/B155)</f>
-        <v/>
-      </c>
-      <c r="E156">
-        <f>LN(C156/C155)</f>
-        <v/>
+      <c r="D156" t="n">
+        <v>0.03875940651971226</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.05592031341076917</v>
       </c>
     </row>
     <row r="157">
@@ -3894,13 +3592,11 @@
       <c r="C157" t="n">
         <v>155.74</v>
       </c>
-      <c r="D157">
-        <f>LN(B157/B156)</f>
-        <v/>
-      </c>
-      <c r="E157">
-        <f>LN(C157/C156)</f>
-        <v/>
+      <c r="D157" t="n">
+        <v>-0.03402743166448301</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-0.1181844260781752</v>
       </c>
     </row>
     <row r="158">
@@ -3913,13 +3609,11 @@
       <c r="C158" t="n">
         <v>138.38</v>
       </c>
-      <c r="D158">
-        <f>LN(B158/B157)</f>
-        <v/>
-      </c>
-      <c r="E158">
-        <f>LN(C158/C157)</f>
-        <v/>
+      <c r="D158" t="n">
+        <v>0.0573044178353546</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.07862976735491765</v>
       </c>
     </row>
     <row r="159">
@@ -3932,13 +3626,11 @@
       <c r="C159" t="n">
         <v>149.7</v>
       </c>
-      <c r="D159">
-        <f>LN(B159/B158)</f>
-        <v/>
-      </c>
-      <c r="E159">
-        <f>LN(C159/C158)</f>
-        <v/>
+      <c r="D159" t="n">
+        <v>-0.006933695523010699</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.01056523333116088</v>
       </c>
     </row>
     <row r="160">
@@ -3951,13 +3643,11 @@
       <c r="C160" t="n">
         <v>151.29</v>
       </c>
-      <c r="D160">
-        <f>LN(B160/B159)</f>
-        <v/>
-      </c>
-      <c r="E160">
-        <f>LN(C160/C159)</f>
-        <v/>
+      <c r="D160" t="n">
+        <v>0.01521153130699479</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-0.02124328381786227</v>
       </c>
     </row>
     <row r="161">
@@ -3970,13 +3660,11 @@
       <c r="C161" t="n">
         <v>148.11</v>
       </c>
-      <c r="D161">
-        <f>LN(B161/B160)</f>
-        <v/>
-      </c>
-      <c r="E161">
-        <f>LN(C161/C160)</f>
-        <v/>
+      <c r="D161" t="n">
+        <v>0.01125746963111819</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-0.002027575714899864</v>
       </c>
     </row>
     <row r="162">
@@ -3989,13 +3677,11 @@
       <c r="C162" t="n">
         <v>147.81</v>
       </c>
-      <c r="D162">
-        <f>LN(B162/B161)</f>
-        <v/>
-      </c>
-      <c r="E162">
-        <f>LN(C162/C161)</f>
-        <v/>
+      <c r="D162" t="n">
+        <v>-0.03430729356418639</v>
+      </c>
+      <c r="E162" t="n">
+        <v>-0.03897448137758559</v>
       </c>
     </row>
     <row r="163">
@@ -4008,13 +3694,11 @@
       <c r="C163" t="n">
         <v>142.16</v>
       </c>
-      <c r="D163">
-        <f>LN(B163/B162)</f>
-        <v/>
-      </c>
-      <c r="E163">
-        <f>LN(C163/C162)</f>
-        <v/>
+      <c r="D163" t="n">
+        <v>-0.02106736158676545</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-0.05531463812590579</v>
       </c>
     </row>
     <row r="164">
@@ -4027,13 +3711,11 @@
       <c r="C164" t="n">
         <v>134.51</v>
       </c>
-      <c r="D164">
-        <f>LN(B164/B163)</f>
-        <v/>
-      </c>
-      <c r="E164">
-        <f>LN(C164/C163)</f>
-        <v/>
+      <c r="D164" t="n">
+        <v>-0.001959159695300347</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-0.01989779203533645</v>
       </c>
     </row>
     <row r="165">
@@ -4046,13 +3728,11 @@
       <c r="C165" t="n">
         <v>131.86</v>
       </c>
-      <c r="D165">
-        <f>LN(B165/B164)</f>
-        <v/>
-      </c>
-      <c r="E165">
-        <f>LN(C165/C164)</f>
-        <v/>
+      <c r="D165" t="n">
+        <v>-0.00138463802912128</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-0.01474490979050863</v>
       </c>
     </row>
     <row r="166">
@@ -4065,13 +3745,11 @@
       <c r="C166" t="n">
         <v>129.93</v>
       </c>
-      <c r="D166">
-        <f>LN(B166/B165)</f>
-        <v/>
-      </c>
-      <c r="E166">
-        <f>LN(C166/C165)</f>
-        <v/>
+      <c r="D166" t="n">
+        <v>0.01437206847608476</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-0.002388750895075092</v>
       </c>
     </row>
     <row r="167">
@@ -4084,13 +3762,11 @@
       <c r="C167" t="n">
         <v>129.62</v>
       </c>
-      <c r="D167">
-        <f>LN(B167/B166)</f>
-        <v/>
-      </c>
-      <c r="E167">
-        <f>LN(C167/C166)</f>
-        <v/>
+      <c r="D167" t="n">
+        <v>0.0263526169732942</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.03888832553878212</v>
       </c>
     </row>
     <row r="168">
@@ -4103,13 +3779,11 @@
       <c r="C168" t="n">
         <v>134.76</v>
       </c>
-      <c r="D168">
-        <f>LN(B168/B167)</f>
-        <v/>
-      </c>
-      <c r="E168">
-        <f>LN(C168/C167)</f>
-        <v/>
+      <c r="D168" t="n">
+        <v>-0.006643525821174627</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.02281579364518565</v>
       </c>
     </row>
     <row r="169">
@@ -4122,13 +3796,11 @@
       <c r="C169" t="n">
         <v>137.87</v>
       </c>
-      <c r="D169">
-        <f>LN(B169/B168)</f>
-        <v/>
-      </c>
-      <c r="E169">
-        <f>LN(C169/C168)</f>
-        <v/>
+      <c r="D169" t="n">
+        <v>0.02435727271050035</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.05681584249611686</v>
       </c>
     </row>
     <row r="170">
@@ -4141,13 +3813,11 @@
       <c r="C170" t="n">
         <v>145.93</v>
       </c>
-      <c r="D170">
-        <f>LN(B170/B169)</f>
-        <v/>
-      </c>
-      <c r="E170">
-        <f>LN(C170/C169)</f>
-        <v/>
+      <c r="D170" t="n">
+        <v>0.01606460250380662</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.05706704165814577</v>
       </c>
     </row>
     <row r="171">
@@ -4160,13 +3830,11 @@
       <c r="C171" t="n">
         <v>154.5</v>
       </c>
-      <c r="D171">
-        <f>LN(B171/B170)</f>
-        <v/>
-      </c>
-      <c r="E171">
-        <f>LN(C171/C170)</f>
-        <v/>
+      <c r="D171" t="n">
+        <v>-0.01118775146282222</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-0.02284803655010248</v>
       </c>
     </row>
     <row r="172">
@@ -4179,13 +3847,11 @@
       <c r="C172" t="n">
         <v>151.01</v>
       </c>
-      <c r="D172">
-        <f>LN(B172/B171)</f>
-        <v/>
-      </c>
-      <c r="E172">
-        <f>LN(C172/C171)</f>
-        <v/>
+      <c r="D172" t="n">
+        <v>-0.002783508844711093</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.01014635137498108</v>
       </c>
     </row>
     <row r="173">
@@ -4198,13 +3864,11 @@
       <c r="C173" t="n">
         <v>152.55</v>
       </c>
-      <c r="D173">
-        <f>LN(B173/B172)</f>
-        <v/>
-      </c>
-      <c r="E173">
-        <f>LN(C173/C172)</f>
-        <v/>
+      <c r="D173" t="n">
+        <v>-0.0270977541083477</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-0.03903456201112605</v>
       </c>
     </row>
     <row r="174">
@@ -4217,13 +3881,11 @@
       <c r="C174" t="n">
         <v>146.71</v>
       </c>
-      <c r="D174">
-        <f>LN(B174/B173)</f>
-        <v/>
-      </c>
-      <c r="E174">
-        <f>LN(C174/C173)</f>
-        <v/>
+      <c r="D174" t="n">
+        <v>0.01886358780461739</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.02902064342669745</v>
       </c>
     </row>
     <row r="175">
@@ -4236,13 +3898,11 @@
       <c r="C175" t="n">
         <v>151.03</v>
       </c>
-      <c r="D175">
-        <f>LN(B175/B174)</f>
-        <v/>
-      </c>
-      <c r="E175">
-        <f>LN(C175/C174)</f>
-        <v/>
+      <c r="D175" t="n">
+        <v>-0.04656074225908149</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-0.01689353433549598</v>
       </c>
     </row>
     <row r="176">
@@ -4255,13 +3915,11 @@
       <c r="C176" t="n">
         <v>148.5</v>
       </c>
-      <c r="D176">
-        <f>LN(B176/B175)</f>
-        <v/>
-      </c>
-      <c r="E176">
-        <f>LN(C176/C175)</f>
-        <v/>
+      <c r="D176" t="n">
+        <v>0.01415512762761456</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.04284015867649223</v>
       </c>
     </row>
     <row r="177">
@@ -4274,13 +3932,11 @@
       <c r="C177" t="n">
         <v>155</v>
       </c>
-      <c r="D177">
-        <f>LN(B177/B176)</f>
-        <v/>
-      </c>
-      <c r="E177">
-        <f>LN(C177/C176)</f>
-        <v/>
+      <c r="D177" t="n">
+        <v>0.0137812905003356</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.03330997888153286</v>
       </c>
     </row>
     <row r="178">
@@ -4293,13 +3949,11 @@
       <c r="C178" t="n">
         <v>160.25</v>
       </c>
-      <c r="D178">
-        <f>LN(B178/B177)</f>
-        <v/>
-      </c>
-      <c r="E178">
-        <f>LN(C178/C177)</f>
-        <v/>
+      <c r="D178" t="n">
+        <v>0.03423969731392303</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.0286041337647739</v>
       </c>
     </row>
     <row r="179">
@@ -4312,13 +3966,11 @@
       <c r="C179" t="n">
         <v>164.9</v>
       </c>
-      <c r="D179">
-        <f>LN(B179/B178)</f>
-        <v/>
-      </c>
-      <c r="E179">
-        <f>LN(C179/C178)</f>
-        <v/>
+      <c r="D179" t="n">
+        <v>-0.001044516202791351</v>
+      </c>
+      <c r="E179" t="n">
+        <v>-0.001456487695273359</v>
       </c>
     </row>
     <row r="180">
@@ -4331,13 +3983,11 @@
       <c r="C180" t="n">
         <v>164.66</v>
       </c>
-      <c r="D180">
-        <f>LN(B180/B179)</f>
-        <v/>
-      </c>
-      <c r="E180">
-        <f>LN(C180/C179)</f>
-        <v/>
+      <c r="D180" t="n">
+        <v>0.007914961989024472</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.003334650072219818</v>
       </c>
     </row>
     <row r="181">
@@ -4350,13 +4000,11 @@
       <c r="C181" t="n">
         <v>165.21</v>
       </c>
-      <c r="D181">
-        <f>LN(B181/B180)</f>
-        <v/>
-      </c>
-      <c r="E181">
-        <f>LN(C181/C180)</f>
-        <v/>
+      <c r="D181" t="n">
+        <v>-0.0009962327752700074</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-0.00115071326630262</v>
       </c>
     </row>
     <row r="182">
@@ -4369,13 +4017,11 @@
       <c r="C182" t="n">
         <v>165.02</v>
       </c>
-      <c r="D182">
-        <f>LN(B182/B181)</f>
-        <v/>
-      </c>
-      <c r="E182">
-        <f>LN(C182/C181)</f>
-        <v/>
+      <c r="D182" t="n">
+        <v>0.008661983581716604</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.02784763158022983</v>
       </c>
     </row>
     <row r="183">
@@ -4388,13 +4034,11 @@
       <c r="C183" t="n">
         <v>169.68</v>
       </c>
-      <c r="D183">
-        <f>LN(B183/B182)</f>
-        <v/>
-      </c>
-      <c r="E183">
-        <f>LN(C183/C182)</f>
-        <v/>
+      <c r="D183" t="n">
+        <v>-0.008001747541495659</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.02266666597636316</v>
       </c>
     </row>
     <row r="184">
@@ -4407,13 +4051,11 @@
       <c r="C184" t="n">
         <v>173.57</v>
       </c>
-      <c r="D184">
-        <f>LN(B184/B183)</f>
-        <v/>
-      </c>
-      <c r="E184">
-        <f>LN(C184/C183)</f>
-        <v/>
+      <c r="D184" t="n">
+        <v>-0.002946615645027543</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-0.005778024973302701</v>
       </c>
     </row>
     <row r="185">
@@ -4426,13 +4068,11 @@
       <c r="C185" t="n">
         <v>172.57</v>
       </c>
-      <c r="D185">
-        <f>LN(B185/B184)</f>
-        <v/>
-      </c>
-      <c r="E185">
-        <f>LN(C185/C184)</f>
-        <v/>
+      <c r="D185" t="n">
+        <v>0.0163302114063361</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.01489689067371013</v>
       </c>
     </row>
     <row r="186">
@@ -4445,13 +4085,11 @@
       <c r="C186" t="n">
         <v>175.16</v>
       </c>
-      <c r="D186">
-        <f>LN(B186/B185)</f>
-        <v/>
-      </c>
-      <c r="E186">
-        <f>LN(C186/C185)</f>
-        <v/>
+      <c r="D186" t="n">
+        <v>0.003208127141960858</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.001540261007895869</v>
       </c>
     </row>
     <row r="187">
@@ -4464,13 +4102,11 @@
       <c r="C187" t="n">
         <v>175.43</v>
       </c>
-      <c r="D187">
-        <f>LN(B187/B186)</f>
-        <v/>
-      </c>
-      <c r="E187">
-        <f>LN(C187/C186)</f>
-        <v/>
+      <c r="D187" t="n">
+        <v>0.01812529149801948</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.03098064706865791</v>
       </c>
     </row>
     <row r="188">
@@ -4483,13 +4119,11 @@
       <c r="C188" t="n">
         <v>180.95</v>
       </c>
-      <c r="D188">
-        <f>LN(B188/B187)</f>
-        <v/>
-      </c>
-      <c r="E188">
-        <f>LN(C188/C187)</f>
-        <v/>
+      <c r="D188" t="n">
+        <v>0.003843276615940024</v>
+      </c>
+      <c r="E188" t="n">
+        <v>5.526235805904471e-05</v>
       </c>
     </row>
     <row r="189">
@@ -4502,13 +4136,11 @@
       <c r="C189" t="n">
         <v>180.96</v>
       </c>
-      <c r="D189">
-        <f>LN(B189/B188)</f>
-        <v/>
-      </c>
-      <c r="E189">
-        <f>LN(C189/C188)</f>
-        <v/>
+      <c r="D189" t="n">
+        <v>0.02543184334427228</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.02164728675221424</v>
       </c>
     </row>
     <row r="190">
@@ -4521,13 +4153,11 @@
       <c r="C190" t="n">
         <v>184.92</v>
       </c>
-      <c r="D190">
-        <f>LN(B190/B189)</f>
-        <v/>
-      </c>
-      <c r="E190">
-        <f>LN(C190/C189)</f>
-        <v/>
+      <c r="D190" t="n">
+        <v>-0.01398985127213033</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.009472621961590363</v>
       </c>
     </row>
     <row r="191">
@@ -4540,13 +4170,11 @@
       <c r="C191" t="n">
         <v>186.68</v>
       </c>
-      <c r="D191">
-        <f>LN(B191/B190)</f>
-        <v/>
-      </c>
-      <c r="E191">
-        <f>LN(C191/C190)</f>
-        <v/>
+      <c r="D191" t="n">
+        <v>0.02319762244772351</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.03830758684858535</v>
       </c>
     </row>
     <row r="192">
@@ -4559,13 +4187,11 @@
       <c r="C192" t="n">
         <v>193.97</v>
       </c>
-      <c r="D192">
-        <f>LN(B192/B191)</f>
-        <v/>
-      </c>
-      <c r="E192">
-        <f>LN(C192/C191)</f>
-        <v/>
+      <c r="D192" t="n">
+        <v>-0.0116236097083878</v>
+      </c>
+      <c r="E192" t="n">
+        <v>-0.01710687759357539</v>
       </c>
     </row>
     <row r="193">
@@ -4578,13 +4204,11 @@
       <c r="C193" t="n">
         <v>190.68</v>
       </c>
-      <c r="D193">
-        <f>LN(B193/B192)</f>
-        <v/>
-      </c>
-      <c r="E193">
-        <f>LN(C193/C192)</f>
-        <v/>
+      <c r="D193" t="n">
+        <v>0.02391524037701544</v>
+      </c>
+      <c r="E193" t="n">
+        <v>5.244250991042422e-05</v>
       </c>
     </row>
     <row r="194">
@@ -4597,13 +4221,11 @@
       <c r="C194" t="n">
         <v>190.69</v>
       </c>
-      <c r="D194">
-        <f>LN(B194/B193)</f>
-        <v/>
-      </c>
-      <c r="E194">
-        <f>LN(C194/C193)</f>
-        <v/>
+      <c r="D194" t="n">
+        <v>0.006839403065279734</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.006533750342946131</v>
       </c>
     </row>
     <row r="195">
@@ -4616,13 +4238,11 @@
       <c r="C195" t="n">
         <v>191.94</v>
       </c>
-      <c r="D195">
-        <f>LN(B195/B194)</f>
-        <v/>
-      </c>
-      <c r="E195">
-        <f>LN(C195/C194)</f>
-        <v/>
+      <c r="D195" t="n">
+        <v>0.01006525966759605</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.0200641127392634</v>
       </c>
     </row>
     <row r="196">
@@ -4635,13 +4255,11 @@
       <c r="C196" t="n">
         <v>195.83</v>
       </c>
-      <c r="D196">
-        <f>LN(B196/B195)</f>
-        <v/>
-      </c>
-      <c r="E196">
-        <f>LN(C196/C195)</f>
-        <v/>
+      <c r="D196" t="n">
+        <v>-0.02300256161877679</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-0.07329519541642951</v>
       </c>
     </row>
     <row r="197">
@@ -4654,13 +4272,11 @@
       <c r="C197" t="n">
         <v>181.99</v>
       </c>
-      <c r="D197">
-        <f>LN(B197/B196)</f>
-        <v/>
-      </c>
-      <c r="E197">
-        <f>LN(C197/C196)</f>
-        <v/>
+      <c r="D197" t="n">
+        <v>-0.003126791840377456</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-0.02334866198383525</v>
       </c>
     </row>
     <row r="198">
@@ -4673,13 +4289,11 @@
       <c r="C198" t="n">
         <v>177.79</v>
       </c>
-      <c r="D198">
-        <f>LN(B198/B197)</f>
-        <v/>
-      </c>
-      <c r="E198">
-        <f>LN(C198/C197)</f>
-        <v/>
+      <c r="D198" t="n">
+        <v>-0.02135978038371894</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-0.01873564511834159</v>
       </c>
     </row>
     <row r="199">
@@ -4692,13 +4306,11 @@
       <c r="C199" t="n">
         <v>174.49</v>
       </c>
-      <c r="D199">
-        <f>LN(B199/B198)</f>
-        <v/>
-      </c>
-      <c r="E199">
-        <f>LN(C199/C198)</f>
-        <v/>
+      <c r="D199" t="n">
+        <v>0.008204781527287172</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.02333722450625352</v>
       </c>
     </row>
     <row r="200">
@@ -4711,13 +4323,11 @@
       <c r="C200" t="n">
         <v>178.61</v>
       </c>
-      <c r="D200">
-        <f>LN(B200/B199)</f>
-        <v/>
-      </c>
-      <c r="E200">
-        <f>LN(C200/C199)</f>
-        <v/>
+      <c r="D200" t="n">
+        <v>0.02467428808716933</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.05897326253099611</v>
       </c>
     </row>
     <row r="201">
@@ -4730,13 +4340,11 @@
       <c r="C201" t="n">
         <v>189.46</v>
       </c>
-      <c r="D201">
-        <f>LN(B201/B200)</f>
-        <v/>
-      </c>
-      <c r="E201">
-        <f>LN(C201/C200)</f>
-        <v/>
+      <c r="D201" t="n">
+        <v>-0.01298988762120686</v>
+      </c>
+      <c r="E201" t="n">
+        <v>-0.06138364515489075</v>
       </c>
     </row>
     <row r="202">
@@ -4749,13 +4357,11 @@
       <c r="C202" t="n">
         <v>178.18</v>
       </c>
-      <c r="D202">
-        <f>LN(B202/B201)</f>
-        <v/>
-      </c>
-      <c r="E202">
-        <f>LN(C202/C201)</f>
-        <v/>
+      <c r="D202" t="n">
+        <v>-0.00160982363755864</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-0.0179511601444318</v>
       </c>
     </row>
     <row r="203">
@@ -4768,13 +4374,11 @@
       <c r="C203" t="n">
         <v>175.01</v>
       </c>
-      <c r="D203">
-        <f>LN(B203/B202)</f>
-        <v/>
-      </c>
-      <c r="E203">
-        <f>LN(C203/C202)</f>
-        <v/>
+      <c r="D203" t="n">
+        <v>-0.029706712656642</v>
+      </c>
+      <c r="E203" t="n">
+        <v>-0.001257861801070893</v>
       </c>
     </row>
     <row r="204">
@@ -4787,13 +4391,11 @@
       <c r="C204" t="n">
         <v>174.79</v>
       </c>
-      <c r="D204">
-        <f>LN(B204/B203)</f>
-        <v/>
-      </c>
-      <c r="E204">
-        <f>LN(C204/C203)</f>
-        <v/>
+      <c r="D204" t="n">
+        <v>-0.007437206900178579</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-0.02069438013026861</v>
       </c>
     </row>
     <row r="205">
@@ -4806,13 +4408,11 @@
       <c r="C205" t="n">
         <v>171.21</v>
       </c>
-      <c r="D205">
-        <f>LN(B205/B204)</f>
-        <v/>
-      </c>
-      <c r="E205">
-        <f>LN(C205/C204)</f>
-        <v/>
+      <c r="D205" t="n">
+        <v>0.004757731549404775</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.03602339608352877</v>
       </c>
     </row>
     <row r="206">
@@ -4825,13 +4425,11 @@
       <c r="C206" t="n">
         <v>177.49</v>
       </c>
-      <c r="D206">
-        <f>LN(B206/B205)</f>
-        <v/>
-      </c>
-      <c r="E206">
-        <f>LN(C206/C205)</f>
-        <v/>
+      <c r="D206" t="n">
+        <v>0.004464892761540559</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.007633196404771485</v>
       </c>
     </row>
     <row r="207">
@@ -4844,13 +4442,11 @@
       <c r="C207" t="n">
         <v>178.85</v>
       </c>
-      <c r="D207">
-        <f>LN(B207/B206)</f>
-        <v/>
-      </c>
-      <c r="E207">
-        <f>LN(C207/C206)</f>
-        <v/>
+      <c r="D207" t="n">
+        <v>-0.02423428398476905</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-0.03394975350639622</v>
       </c>
     </row>
     <row r="208">
@@ -4863,13 +4459,11 @@
       <c r="C208" t="n">
         <v>172.88</v>
       </c>
-      <c r="D208">
-        <f>LN(B208/B207)</f>
-        <v/>
-      </c>
-      <c r="E208">
-        <f>LN(C208/C207)</f>
-        <v/>
+      <c r="D208" t="n">
+        <v>-0.02560581445938402</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-0.02732506566433933</v>
       </c>
     </row>
     <row r="209">
@@ -4882,13 +4476,11 @@
       <c r="C209" t="n">
         <v>168.22</v>
       </c>
-      <c r="D209">
-        <f>LN(B209/B208)</f>
-        <v/>
-      </c>
-      <c r="E209">
-        <f>LN(C209/C208)</f>
-        <v/>
+      <c r="D209" t="n">
+        <v>0.05687664090334639</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.04889772727086309</v>
       </c>
     </row>
     <row r="210">
@@ -4901,13 +4493,11 @@
       <c r="C210" t="n">
         <v>176.65</v>
       </c>
-      <c r="D210">
-        <f>LN(B210/B209)</f>
-        <v/>
-      </c>
-      <c r="E210">
-        <f>LN(C210/C209)</f>
-        <v/>
+      <c r="D210" t="n">
+        <v>0.01297094179594674</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.05372452844633653</v>
       </c>
     </row>
     <row r="211">
@@ -4920,13 +4510,11 @@
       <c r="C211" t="n">
         <v>186.4</v>
       </c>
-      <c r="D211">
-        <f>LN(B211/B210)</f>
-        <v/>
-      </c>
-      <c r="E211">
-        <f>LN(C211/C210)</f>
-        <v/>
+      <c r="D211" t="n">
+        <v>0.02212591633133202</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.0174962584871406</v>
       </c>
     </row>
     <row r="212">
@@ -4939,13 +4527,11 @@
       <c r="C212" t="n">
         <v>189.69</v>
       </c>
-      <c r="D212">
-        <f>LN(B212/B211)</f>
-        <v/>
-      </c>
-      <c r="E212">
-        <f>LN(C212/C211)</f>
-        <v/>
+      <c r="D212" t="n">
+        <v>0.009989767163104797</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.001475004218326301</v>
       </c>
     </row>
     <row r="213">
@@ -4958,13 +4544,11 @@
       <c r="C213" t="n">
         <v>189.97</v>
       </c>
-      <c r="D213">
-        <f>LN(B213/B212)</f>
-        <v/>
-      </c>
-      <c r="E213">
-        <f>LN(C213/C212)</f>
-        <v/>
+      <c r="D213" t="n">
+        <v>0.007710354049898103</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.00666301880094491</v>
       </c>
     </row>
     <row r="214">
@@ -4977,13 +4561,11 @@
       <c r="C214" t="n">
         <v>191.24</v>
       </c>
-      <c r="D214">
-        <f>LN(B214/B213)</f>
-        <v/>
-      </c>
-      <c r="E214">
-        <f>LN(C214/C213)</f>
-        <v/>
+      <c r="D214" t="n">
+        <v>0.002117622271937392</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.02310478795897512</v>
       </c>
     </row>
     <row r="215">
@@ -4996,13 +4578,11 @@
       <c r="C215" t="n">
         <v>195.71</v>
       </c>
-      <c r="D215">
-        <f>LN(B215/B214)</f>
-        <v/>
-      </c>
-      <c r="E215">
-        <f>LN(C215/C214)</f>
-        <v/>
+      <c r="D215" t="n">
+        <v>0.02463132217062493</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.009458980208435755</v>
       </c>
     </row>
     <row r="216">
@@ -5015,13 +4595,11 @@
       <c r="C216" t="n">
         <v>197.57</v>
       </c>
-      <c r="D216">
-        <f>LN(B216/B215)</f>
-        <v/>
-      </c>
-      <c r="E216">
-        <f>LN(C216/C215)</f>
-        <v/>
+      <c r="D216" t="n">
+        <v>0.007481705439914485</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-0.0202987770828371</v>
       </c>
     </row>
     <row r="217">
@@ -5034,13 +4612,11 @@
       <c r="C217" t="n">
         <v>193.6</v>
       </c>
-      <c r="D217">
-        <f>LN(B217/B216)</f>
-        <v/>
-      </c>
-      <c r="E217">
-        <f>LN(C217/C216)</f>
-        <v/>
+      <c r="D217" t="n">
+        <v>0.003191784710975985</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-0.005542189101232491</v>
       </c>
     </row>
     <row r="218">
@@ -5053,13 +4629,11 @@
       <c r="C218" t="n">
         <v>192.53</v>
       </c>
-      <c r="D218">
-        <f>LN(B218/B217)</f>
-        <v/>
-      </c>
-      <c r="E218">
-        <f>LN(C218/C217)</f>
-        <v/>
+      <c r="D218" t="n">
+        <v>-0.01533556266813473</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-0.06076097350010235</v>
       </c>
     </row>
     <row r="219">
@@ -5072,13 +4646,11 @@
       <c r="C219" t="n">
         <v>181.18</v>
       </c>
-      <c r="D219">
-        <f>LN(B219/B218)</f>
-        <v/>
-      </c>
-      <c r="E219">
-        <f>LN(C219/C218)</f>
-        <v/>
+      <c r="D219" t="n">
+        <v>0.01826637871586836</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.02582546142240448</v>
       </c>
     </row>
     <row r="220">
@@ -5091,13 +4663,11 @@
       <c r="C220" t="n">
         <v>185.92</v>
       </c>
-      <c r="D220">
-        <f>LN(B220/B219)</f>
-        <v/>
-      </c>
-      <c r="E220">
-        <f>LN(C220/C219)</f>
-        <v/>
+      <c r="D220" t="n">
+        <v>0.01163398285976206</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.0298846018108622</v>
       </c>
     </row>
     <row r="221">
@@ -5110,13 +4680,11 @@
       <c r="C221" t="n">
         <v>191.56</v>
       </c>
-      <c r="D221">
-        <f>LN(B221/B220)</f>
-        <v/>
-      </c>
-      <c r="E221">
-        <f>LN(C221/C220)</f>
-        <v/>
+      <c r="D221" t="n">
+        <v>0.01051518406377356</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.004479407458709794</v>
       </c>
     </row>
     <row r="222">
@@ -5129,13 +4697,11 @@
       <c r="C222" t="n">
         <v>192.42</v>
       </c>
-      <c r="D222">
-        <f>LN(B222/B221)</f>
-        <v/>
-      </c>
-      <c r="E222">
-        <f>LN(C222/C221)</f>
-        <v/>
+      <c r="D222" t="n">
+        <v>0.01373481170282096</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-0.03474058618985738</v>
       </c>
     </row>
     <row r="223">
@@ -5148,13 +4714,11 @@
       <c r="C223" t="n">
         <v>185.85</v>
       </c>
-      <c r="D223">
-        <f>LN(B223/B222)</f>
-        <v/>
-      </c>
-      <c r="E223">
-        <f>LN(C223/C222)</f>
-        <v/>
+      <c r="D223" t="n">
+        <v>0.01362034111236493</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.01601315241520467</v>
       </c>
     </row>
     <row r="224">
@@ -5167,13 +4731,11 @@
       <c r="C224" t="n">
         <v>188.85</v>
       </c>
-      <c r="D224">
-        <f>LN(B224/B223)</f>
-        <v/>
-      </c>
-      <c r="E224">
-        <f>LN(C224/C223)</f>
-        <v/>
+      <c r="D224" t="n">
+        <v>-0.004194508242069255</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-0.03524451434309223</v>
       </c>
     </row>
     <row r="225">
@@ -5186,13 +4748,11 @@
       <c r="C225" t="n">
         <v>182.31</v>
       </c>
-      <c r="D225">
-        <f>LN(B225/B224)</f>
-        <v/>
-      </c>
-      <c r="E225">
-        <f>LN(C225/C224)</f>
-        <v/>
+      <c r="D225" t="n">
+        <v>0.0164907539859186</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.001151221243828195</v>
       </c>
     </row>
     <row r="226">
@@ -5205,13 +4765,11 @@
       <c r="C226" t="n">
         <v>182.52</v>
       </c>
-      <c r="D226">
-        <f>LN(B226/B225)</f>
-        <v/>
-      </c>
-      <c r="E226">
-        <f>LN(C226/C225)</f>
-        <v/>
+      <c r="D226" t="n">
+        <v>0.009442778273215388</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-0.01579358025814135</v>
       </c>
     </row>
     <row r="227">
@@ -5224,13 +4782,11 @@
       <c r="C227" t="n">
         <v>179.66</v>
       </c>
-      <c r="D227">
-        <f>LN(B227/B226)</f>
-        <v/>
-      </c>
-      <c r="E227">
-        <f>LN(C227/C226)</f>
-        <v/>
+      <c r="D227" t="n">
+        <v>-0.002609942061040329</v>
+      </c>
+      <c r="E227" t="n">
+        <v>-0.0509828145179184</v>
       </c>
     </row>
     <row r="228">
@@ -5243,13 +4799,11 @@
       <c r="C228" t="n">
         <v>170.73</v>
       </c>
-      <c r="D228">
-        <f>LN(B228/B227)</f>
-        <v/>
-      </c>
-      <c r="E228">
-        <f>LN(C228/C227)</f>
-        <v/>
+      <c r="D228" t="n">
+        <v>-0.001288964495631342</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.0110092855083694</v>
       </c>
     </row>
     <row r="229">
@@ -5262,13 +4816,11 @@
       <c r="C229" t="n">
         <v>172.62</v>
       </c>
-      <c r="D229">
-        <f>LN(B229/B228)</f>
-        <v/>
-      </c>
-      <c r="E229">
-        <f>LN(C229/C228)</f>
-        <v/>
+      <c r="D229" t="n">
+        <v>0.02262427594111255</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-0.001971586605601786</v>
       </c>
     </row>
     <row r="230">
@@ -5281,13 +4833,11 @@
       <c r="C230" t="n">
         <v>172.28</v>
       </c>
-      <c r="D230">
-        <f>LN(B230/B229)</f>
-        <v/>
-      </c>
-      <c r="E230">
-        <f>LN(C230/C229)</f>
-        <v/>
+      <c r="D230" t="n">
+        <v>0.003846110916179418</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-0.004654418456133513</v>
       </c>
     </row>
     <row r="231">
@@ -5300,13 +4850,11 @@
       <c r="C231" t="n">
         <v>171.48</v>
       </c>
-      <c r="D231">
-        <f>LN(B231/B230)</f>
-        <v/>
-      </c>
-      <c r="E231">
-        <f>LN(C231/C230)</f>
-        <v/>
+      <c r="D231" t="n">
+        <v>-0.00956341208204454</v>
+      </c>
+      <c r="E231" t="n">
+        <v>-0.01114184985391922</v>
       </c>
     </row>
     <row r="232">
@@ -5319,13 +4867,11 @@
       <c r="C232" t="n">
         <v>169.58</v>
       </c>
-      <c r="D232">
-        <f>LN(B232/B231)</f>
-        <v/>
-      </c>
-      <c r="E232">
-        <f>LN(C232/C231)</f>
-        <v/>
+      <c r="D232" t="n">
+        <v>-0.01567265988781149</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.04027933049853856</v>
       </c>
     </row>
     <row r="233">
@@ -5338,13 +4884,11 @@
       <c r="C233" t="n">
         <v>176.55</v>
       </c>
-      <c r="D233">
-        <f>LN(B233/B232)</f>
-        <v/>
-      </c>
-      <c r="E233">
-        <f>LN(C233/C232)</f>
-        <v/>
+      <c r="D233" t="n">
+        <v>-0.03095789231622316</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-0.06765864847381481</v>
       </c>
     </row>
     <row r="234">
@@ -5357,13 +4901,11 @@
       <c r="C234" t="n">
         <v>165</v>
       </c>
-      <c r="D234">
-        <f>LN(B234/B233)</f>
-        <v/>
-      </c>
-      <c r="E234">
-        <f>LN(C234/C233)</f>
-        <v/>
+      <c r="D234" t="n">
+        <v>0.02637035589205366</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.02572681523850908</v>
       </c>
     </row>
     <row r="235">
@@ -5376,13 +4918,11 @@
       <c r="C235" t="n">
         <v>169.3</v>
       </c>
-      <c r="D235">
-        <f>LN(B235/B234)</f>
-        <v/>
-      </c>
-      <c r="E235">
-        <f>LN(C235/C234)</f>
-        <v/>
+      <c r="D235" t="n">
+        <v>0.005442070579494519</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.07988821348266507</v>
       </c>
     </row>
     <row r="236">
@@ -5395,13 +4935,11 @@
       <c r="C236" t="n">
         <v>183.38</v>
       </c>
-      <c r="D236">
-        <f>LN(B236/B235)</f>
-        <v/>
-      </c>
-      <c r="E236">
-        <f>LN(C236/C235)</f>
-        <v/>
+      <c r="D236" t="n">
+        <v>0.01833591296466925</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-0.00180116305550943</v>
       </c>
     </row>
     <row r="237">
@@ -5414,13 +4952,11 @@
       <c r="C237" t="n">
         <v>183.05</v>
       </c>
-      <c r="D237">
-        <f>LN(B237/B236)</f>
-        <v/>
-      </c>
-      <c r="E237">
-        <f>LN(C237/C236)</f>
-        <v/>
+      <c r="D237" t="n">
+        <v>0.01531293132911324</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.0365802878890784</v>
       </c>
     </row>
     <row r="238">
@@ -5433,13 +4969,11 @@
       <c r="C238" t="n">
         <v>189.87</v>
       </c>
-      <c r="D238">
-        <f>LN(B238/B237)</f>
-        <v/>
-      </c>
-      <c r="E238">
-        <f>LN(C238/C237)</f>
-        <v/>
+      <c r="D238" t="n">
+        <v>0.0002733788416148375</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.0005791760067125792</v>
       </c>
     </row>
     <row r="239">
@@ -5452,13 +4986,11 @@
       <c r="C239" t="n">
         <v>189.98</v>
       </c>
-      <c r="D239">
-        <f>LN(B239/B238)</f>
-        <v/>
-      </c>
-      <c r="E239">
-        <f>LN(C239/C238)</f>
-        <v/>
+      <c r="D239" t="n">
+        <v>-0.005142594702045587</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.01187780492371692</v>
       </c>
     </row>
     <row r="240">
@@ -5471,13 +5003,11 @@
       <c r="C240" t="n">
         <v>192.25</v>
       </c>
-      <c r="D240">
-        <f>LN(B240/B239)</f>
-        <v/>
-      </c>
-      <c r="E240">
-        <f>LN(C240/C239)</f>
-        <v/>
+      <c r="D240" t="n">
+        <v>0.01307939018213883</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.0238485887679876</v>
       </c>
     </row>
     <row r="241">
@@ -5490,13 +5020,11 @@
       <c r="C241" t="n">
         <v>196.89</v>
       </c>
-      <c r="D241">
-        <f>LN(B241/B240)</f>
-        <v/>
-      </c>
-      <c r="E241">
-        <f>LN(C241/C240)</f>
-        <v/>
+      <c r="D241" t="n">
+        <v>0.01569996408525012</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.07624973127989988</v>
       </c>
     </row>
     <row r="242">
@@ -5509,13 +5037,11 @@
       <c r="C242" t="n">
         <v>212.49</v>
       </c>
-      <c r="D242">
-        <f>LN(B242/B241)</f>
-        <v/>
-      </c>
-      <c r="E242">
-        <f>LN(C242/C241)</f>
-        <v/>
+      <c r="D242" t="n">
+        <v>0.006060835974113174</v>
+      </c>
+      <c r="E242" t="n">
+        <v>-0.0238117826952812</v>
       </c>
     </row>
     <row r="243">
@@ -5528,13 +5054,11 @@
       <c r="C243" t="n">
         <v>207.49</v>
       </c>
-      <c r="D243">
-        <f>LN(B243/B242)</f>
-        <v/>
-      </c>
-      <c r="E243">
-        <f>LN(C243/C242)</f>
-        <v/>
+      <c r="D243" t="n">
+        <v>-0.0007578878359311989</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.01497241621409132</v>
       </c>
     </row>
     <row r="244">
@@ -5547,13 +5071,11 @@
       <c r="C244" t="n">
         <v>210.62</v>
       </c>
-      <c r="D244">
-        <f>LN(B244/B243)</f>
-        <v/>
-      </c>
-      <c r="E244">
-        <f>LN(C244/C243)</f>
-        <v/>
+      <c r="D244" t="n">
+        <v>0.0193537403311141</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.0719827315853445</v>
       </c>
     </row>
     <row r="245">
@@ -5566,13 +5088,11 @@
       <c r="C245" t="n">
         <v>226.34</v>
       </c>
-      <c r="D245">
-        <f>LN(B245/B244)</f>
-        <v/>
-      </c>
-      <c r="E245">
-        <f>LN(C245/C244)</f>
-        <v/>
+      <c r="D245" t="n">
+        <v>0.008613480972494184</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.01838608963507094</v>
       </c>
     </row>
     <row r="246">
@@ -5585,13 +5105,11 @@
       <c r="C246" t="n">
         <v>230.54</v>
       </c>
-      <c r="D246">
-        <f>LN(B246/B245)</f>
-        <v/>
-      </c>
-      <c r="E246">
-        <f>LN(C246/C245)</f>
-        <v/>
+      <c r="D246" t="n">
+        <v>-0.01984714910964965</v>
+      </c>
+      <c r="E246" t="n">
+        <v>-0.02739535949293256</v>
       </c>
     </row>
     <row r="247">
@@ -5604,13 +5122,11 @@
       <c r="C247" t="n">
         <v>224.31</v>
       </c>
-      <c r="D247">
-        <f>LN(B247/B246)</f>
-        <v/>
-      </c>
-      <c r="E247">
-        <f>LN(C247/C246)</f>
-        <v/>
+      <c r="D247" t="n">
+        <v>-0.008372829169473591</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-0.02871746396503629</v>
       </c>
     </row>
     <row r="248">
@@ -5623,13 +5139,11 @@
       <c r="C248" t="n">
         <v>217.96</v>
       </c>
-      <c r="D248">
-        <f>LN(B248/B247)</f>
-        <v/>
-      </c>
-      <c r="E248">
-        <f>LN(C248/C247)</f>
-        <v/>
+      <c r="D248" t="n">
+        <v>-0.02083057755860555</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0.008679420435820037</v>
       </c>
     </row>
     <row r="249">
@@ -5642,13 +5156,11 @@
       <c r="C249" t="n">
         <v>219.86</v>
       </c>
-      <c r="D249">
-        <f>LN(B249/B248)</f>
-        <v/>
-      </c>
-      <c r="E249">
-        <f>LN(C249/C248)</f>
-        <v/>
+      <c r="D249" t="n">
+        <v>-0.0004489875406555176</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-0.01660207818252551</v>
       </c>
     </row>
     <row r="250">
@@ -5661,13 +5173,11 @@
       <c r="C250" t="n">
         <v>216.24</v>
       </c>
-      <c r="D250">
-        <f>LN(B250/B249)</f>
-        <v/>
-      </c>
-      <c r="E250">
-        <f>LN(C250/C249)</f>
-        <v/>
+      <c r="D250" t="n">
+        <v>0.03855902456919127</v>
+      </c>
+      <c r="E250" t="n">
+        <v>0.04436731177242196</v>
       </c>
     </row>
     <row r="251">
@@ -5680,13 +5190,11 @@
       <c r="C251" t="n">
         <v>226.05</v>
       </c>
-      <c r="D251">
-        <f>LN(B251/B250)</f>
-        <v/>
-      </c>
-      <c r="E251">
-        <f>LN(C251/C250)</f>
-        <v/>
+      <c r="D251" t="n">
+        <v>0.01436453432868394</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0.003488709405212978</v>
       </c>
     </row>
     <row r="252">
@@ -5699,13 +5207,11 @@
       <c r="C252" t="n">
         <v>226.84</v>
       </c>
-      <c r="D252">
-        <f>LN(B252/B251)</f>
-        <v/>
-      </c>
-      <c r="E252">
-        <f>LN(C252/C251)</f>
-        <v/>
+      <c r="D252" t="n">
+        <v>0.002444384409175766</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.009477080408412275</v>
       </c>
     </row>
     <row r="253">
@@ -5718,13 +5224,11 @@
       <c r="C253" t="n">
         <v>229</v>
       </c>
-      <c r="D253">
-        <f>LN(B253/B252)</f>
-        <v/>
-      </c>
-      <c r="E253">
-        <f>LN(C253/C252)</f>
-        <v/>
+      <c r="D253" t="n">
+        <v>-0.04341532076599641</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-0.03637411354324874</v>
       </c>
     </row>
     <row r="254">
@@ -5737,13 +5241,11 @@
       <c r="C254" t="n">
         <v>220.82</v>
       </c>
-      <c r="D254">
-        <f>LN(B254/B253)</f>
-        <v/>
-      </c>
-      <c r="E254">
-        <f>LN(C254/C253)</f>
-        <v/>
+      <c r="D254" t="n">
+        <v>0.03944526653795214</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0.007579211595304088</v>
       </c>
     </row>
     <row r="255">
@@ -5756,13 +5258,11 @@
       <c r="C255" t="n">
         <v>222.5</v>
       </c>
-      <c r="D255">
-        <f>LN(B255/B254)</f>
-        <v/>
-      </c>
-      <c r="E255">
-        <f>LN(C255/C254)</f>
-        <v/>
+      <c r="D255" t="n">
+        <v>0.01351117823722467</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.02529533582168028</v>
       </c>
     </row>
     <row r="256">
@@ -5775,13 +5275,11 @@
       <c r="C256" t="n">
         <v>228.2</v>
       </c>
-      <c r="D256">
-        <f>LN(B256/B255)</f>
-        <v/>
-      </c>
-      <c r="E256">
-        <f>LN(C256/C255)</f>
-        <v/>
+      <c r="D256" t="n">
+        <v>0.00622690094591228</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-0.001798285534723234</v>
       </c>
     </row>
     <row r="257">
@@ -5794,13 +5292,11 @@
       <c r="C257" t="n">
         <v>227.79</v>
       </c>
-      <c r="D257">
-        <f>LN(B257/B256)</f>
-        <v/>
-      </c>
-      <c r="E257">
-        <f>LN(C257/C256)</f>
-        <v/>
+      <c r="D257" t="n">
+        <v>0.002245580285698136</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-0.004355580039654991</v>
       </c>
     </row>
     <row r="258">
@@ -5813,13 +5309,11 @@
       <c r="C258" t="n">
         <v>226.8</v>
       </c>
-      <c r="D258">
-        <f>LN(B258/B257)</f>
-        <v/>
-      </c>
-      <c r="E258">
-        <f>LN(C258/C257)</f>
-        <v/>
+      <c r="D258" t="n">
+        <v>0.01106002057493614</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.003301422609054003</v>
       </c>
     </row>
     <row r="259">
@@ -5832,13 +5326,11 @@
       <c r="C259" t="n">
         <v>227.55</v>
       </c>
-      <c r="D259">
-        <f>LN(B259/B258)</f>
-        <v/>
-      </c>
-      <c r="E259">
-        <f>LN(C259/C258)</f>
-        <v/>
+      <c r="D259" t="n">
+        <v>0.008500269509107226</v>
+      </c>
+      <c r="E259" t="n">
+        <v>0.03221551968150791</v>
       </c>
     </row>
     <row r="260">
@@ -5851,13 +5343,11 @@
       <c r="C260" t="n">
         <v>235</v>
       </c>
-      <c r="D260">
-        <f>LN(B260/B259)</f>
-        <v/>
-      </c>
-      <c r="E260">
-        <f>LN(C260/C259)</f>
-        <v/>
+      <c r="D260" t="n">
+        <v>-0.009689276071713221</v>
+      </c>
+      <c r="E260" t="n">
+        <v>-0.01539448510657861</v>
       </c>
     </row>
     <row r="261">
@@ -5870,13 +5360,11 @@
       <c r="C261" t="n">
         <v>231.41</v>
       </c>
-      <c r="D261">
-        <f>LN(B261/B260)</f>
-        <v/>
-      </c>
-      <c r="E261">
-        <f>LN(C261/C260)</f>
-        <v/>
+      <c r="D261" t="n">
+        <v>-0.01375085375548801</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-0.03742292648473936</v>
       </c>
     </row>
     <row r="262">
@@ -5889,13 +5377,11 @@
       <c r="C262" t="n">
         <v>222.91</v>
       </c>
-      <c r="D262">
-        <f>LN(B262/B261)</f>
-        <v/>
-      </c>
-      <c r="E262">
-        <f>LN(C262/C261)</f>
-        <v/>
+      <c r="D262" t="n">
+        <v>0.04550977477492174</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.01800568794775506</v>
       </c>
     </row>
     <row r="263">
@@ -5908,13 +5394,11 @@
       <c r="C263" t="n">
         <v>226.96</v>
       </c>
-      <c r="D263">
-        <f>LN(B263/B262)</f>
-        <v/>
-      </c>
-      <c r="E263">
-        <f>LN(C263/C262)</f>
-        <v/>
+      <c r="D263" t="n">
+        <v>-0.02105560941730776</v>
+      </c>
+      <c r="E263" t="n">
+        <v>-0.008673388296175855</v>
       </c>
     </row>
     <row r="264">
@@ -5927,13 +5411,11 @@
       <c r="C264" t="n">
         <v>225</v>
       </c>
-      <c r="D264">
-        <f>LN(B264/B263)</f>
-        <v/>
-      </c>
-      <c r="E264">
-        <f>LN(C264/C263)</f>
-        <v/>
+      <c r="D264" t="n">
+        <v>0.01667611846107745</v>
+      </c>
+      <c r="E264" t="n">
+        <v>0.02141352953190543</v>
       </c>
     </row>
     <row r="265">
@@ -5946,13 +5428,11 @@
       <c r="C265" t="n">
         <v>229.87</v>
       </c>
-      <c r="D265">
-        <f>LN(B265/B264)</f>
-        <v/>
-      </c>
-      <c r="E265">
-        <f>LN(C265/C264)</f>
-        <v/>
+      <c r="D265" t="n">
+        <v>0.01050525753960101</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0.03193764596508905</v>
       </c>
     </row>
     <row r="266">
@@ -5965,13 +5445,11 @@
       <c r="C266" t="n">
         <v>237.33</v>
       </c>
-      <c r="D266">
-        <f>LN(B266/B265)</f>
-        <v/>
-      </c>
-      <c r="E266">
-        <f>LN(C266/C265)</f>
-        <v/>
+      <c r="D266" t="n">
+        <v>0.009550789645523784</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.02295121256081857</v>
       </c>
     </row>
     <row r="267">
@@ -5984,13 +5462,11 @@
       <c r="C267" t="n">
         <v>242.84</v>
       </c>
-      <c r="D267">
-        <f>LN(B267/B266)</f>
-        <v/>
-      </c>
-      <c r="E267">
-        <f>LN(C267/C266)</f>
-        <v/>
+      <c r="D267" t="n">
+        <v>-0.006453994610219541</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0.02155001210969133</v>
       </c>
     </row>
     <row r="268">
@@ -6003,13 +5479,11 @@
       <c r="C268" t="n">
         <v>248.13</v>
       </c>
-      <c r="D268">
-        <f>LN(B268/B267)</f>
-        <v/>
-      </c>
-      <c r="E268">
-        <f>LN(C268/C267)</f>
-        <v/>
+      <c r="D268" t="n">
+        <v>-0.02007087941213312</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0.02530874011582836</v>
       </c>
     </row>
     <row r="269">
@@ -6022,13 +5496,11 @@
       <c r="C269" t="n">
         <v>254.49</v>
       </c>
-      <c r="D269">
-        <f>LN(B269/B268)</f>
-        <v/>
-      </c>
-      <c r="E269">
-        <f>LN(C269/C268)</f>
-        <v/>
+      <c r="D269" t="n">
+        <v>0.00672007933223057</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.004313055619604551</v>
       </c>
     </row>
     <row r="270">
@@ -6041,13 +5513,11 @@
       <c r="C270" t="n">
         <v>255.59</v>
       </c>
-      <c r="D270">
-        <f>LN(B270/B269)</f>
-        <v/>
-      </c>
-      <c r="E270">
-        <f>LN(C270/C269)</f>
-        <v/>
+      <c r="D270" t="n">
+        <v>-0.004762749165129663</v>
+      </c>
+      <c r="E270" t="n">
+        <v>-0.04903276959637479</v>
       </c>
     </row>
     <row r="271">
@@ -6060,13 +5530,11 @@
       <c r="C271" t="n">
         <v>243.36</v>
       </c>
-      <c r="D271">
-        <f>LN(B271/B270)</f>
-        <v/>
-      </c>
-      <c r="E271">
-        <f>LN(C271/C270)</f>
-        <v/>
+      <c r="D271" t="n">
+        <v>-0.01961571912593472</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-0.027114799141222</v>
       </c>
     </row>
     <row r="272">
@@ -6079,13 +5547,11 @@
       <c r="C272" t="n">
         <v>236.85</v>
       </c>
-      <c r="D272">
-        <f>LN(B272/B271)</f>
-        <v/>
-      </c>
-      <c r="E272">
-        <f>LN(C272/C271)</f>
-        <v/>
+      <c r="D272" t="n">
+        <v>0.02869349483175312</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-0.02943468074924207</v>
       </c>
     </row>
     <row r="273">
@@ -6098,13 +5564,11 @@
       <c r="C273" t="n">
         <v>229.98</v>
       </c>
-      <c r="D273">
-        <f>LN(B273/B272)</f>
-        <v/>
-      </c>
-      <c r="E273">
-        <f>LN(C273/C272)</f>
-        <v/>
+      <c r="D273" t="n">
+        <v>0.01728938164450116</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-0.0318076112034749</v>
       </c>
     </row>
     <row r="274">
@@ -6117,13 +5581,11 @@
       <c r="C274" t="n">
         <v>222.78</v>
       </c>
-      <c r="D274">
-        <f>LN(B274/B273)</f>
-        <v/>
-      </c>
-      <c r="E274">
-        <f>LN(C274/C273)</f>
-        <v/>
+      <c r="D274" t="n">
+        <v>-0.01000027276804339</v>
+      </c>
+      <c r="E274" t="n">
+        <v>0.05764706760856635</v>
       </c>
     </row>
     <row r="275">
@@ -6136,13 +5598,11 @@
       <c r="C275" t="n">
         <v>236</v>
       </c>
-      <c r="D275">
-        <f>LN(B275/B274)</f>
-        <v/>
-      </c>
-      <c r="E275">
-        <f>LN(C275/C274)</f>
-        <v/>
+      <c r="D275" t="n">
+        <v>-0.002409975210306763</v>
+      </c>
+      <c r="E275" t="n">
+        <v>-0.03611030126631286</v>
       </c>
     </row>
     <row r="276">
@@ -6155,13 +5615,11 @@
       <c r="C276" t="n">
         <v>227.63</v>
       </c>
-      <c r="D276">
-        <f>LN(B276/B275)</f>
-        <v/>
-      </c>
-      <c r="E276">
-        <f>LN(C276/C275)</f>
-        <v/>
+      <c r="D276" t="n">
+        <v>0.01460247912726698</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.07190271949377479</v>
       </c>
     </row>
     <row r="277">
@@ -6174,13 +5632,11 @@
       <c r="C277" t="n">
         <v>244.6</v>
       </c>
-      <c r="D277">
-        <f>LN(B277/B276)</f>
-        <v/>
-      </c>
-      <c r="E277">
-        <f>LN(C277/C276)</f>
-        <v/>
+      <c r="D277" t="n">
+        <v>-0.0167388487109518</v>
+      </c>
+      <c r="E277" t="n">
+        <v>0.003876369232181725</v>
       </c>
     </row>
     <row r="278">
@@ -6193,13 +5649,11 @@
       <c r="C278" t="n">
         <v>245.55</v>
       </c>
-      <c r="D278">
-        <f>LN(B278/B277)</f>
-        <v/>
-      </c>
-      <c r="E278">
-        <f>LN(C278/C277)</f>
-        <v/>
+      <c r="D278" t="n">
+        <v>-0.009798175421528476</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-0.01522424201405104</v>
       </c>
     </row>
     <row r="279">
@@ -6212,13 +5666,11 @@
       <c r="C279" t="n">
         <v>241.84</v>
       </c>
-      <c r="D279">
-        <f>LN(B279/B278)</f>
-        <v/>
-      </c>
-      <c r="E279">
-        <f>LN(C279/C278)</f>
-        <v/>
+      <c r="D279" t="n">
+        <v>-0.0314404942615594</v>
+      </c>
+      <c r="E279" t="n">
+        <v>-0.01151995439343617</v>
       </c>
     </row>
     <row r="280">
@@ -6231,13 +5683,11 @@
       <c r="C280" t="n">
         <v>239.07</v>
       </c>
-      <c r="D280">
-        <f>LN(B280/B279)</f>
-        <v/>
-      </c>
-      <c r="E280">
-        <f>LN(C280/C279)</f>
-        <v/>
+      <c r="D280" t="n">
+        <v>-0.02301063738034607</v>
+      </c>
+      <c r="E280" t="n">
+        <v>-0.1131664029135338</v>
       </c>
     </row>
     <row r="281">
@@ -6250,13 +5700,11 @@
       <c r="C281" t="n">
         <v>213.49</v>
       </c>
-      <c r="D281">
-        <f>LN(B281/B280)</f>
-        <v/>
-      </c>
-      <c r="E281">
-        <f>LN(C281/C280)</f>
-        <v/>
+      <c r="D281" t="n">
+        <v>0.005062585437930187</v>
+      </c>
+      <c r="E281" t="n">
+        <v>0.02214283538675353</v>
       </c>
     </row>
     <row r="282">
@@ -6269,13 +5717,11 @@
       <c r="C282" t="n">
         <v>218.27</v>
       </c>
-      <c r="D282">
-        <f>LN(B282/B281)</f>
-        <v/>
-      </c>
-      <c r="E282">
-        <f>LN(C282/C281)</f>
-        <v/>
+      <c r="D282" t="n">
+        <v>-0.01540146903494393</v>
+      </c>
+      <c r="E282" t="n">
+        <v>-0.001696586600412</v>
       </c>
     </row>
     <row r="283">
@@ -6288,13 +5734,11 @@
       <c r="C283" t="n">
         <v>217.9</v>
       </c>
-      <c r="D283">
-        <f>LN(B283/B282)</f>
-        <v/>
-      </c>
-      <c r="E283">
-        <f>LN(C283/C282)</f>
-        <v/>
+      <c r="D283" t="n">
+        <v>-0.09521199328066883</v>
+      </c>
+      <c r="E283" t="n">
+        <v>-0.1455750425559032</v>
       </c>
     </row>
     <row r="284">
@@ -6307,13 +5751,11 @@
       <c r="C284" t="n">
         <v>188.38</v>
       </c>
-      <c r="D284">
-        <f>LN(B284/B283)</f>
-        <v/>
-      </c>
-      <c r="E284">
-        <f>LN(C284/C283)</f>
-        <v/>
+      <c r="D284" t="n">
+        <v>0.05544541664981416</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.05056312024177304</v>
       </c>
     </row>
     <row r="285">
@@ -6326,13 +5768,11 @@
       <c r="C285" t="n">
         <v>198.15</v>
       </c>
-      <c r="D285">
-        <f>LN(B285/B284)</f>
-        <v/>
-      </c>
-      <c r="E285">
-        <f>LN(C285/C284)</f>
-        <v/>
+      <c r="D285" t="n">
+        <v>-0.01515331370343486</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-0.005922118894887773</v>
       </c>
     </row>
     <row r="286">
@@ -6345,13 +5785,11 @@
       <c r="C286" t="n">
         <v>196.98</v>
       </c>
-      <c r="D286">
-        <f>LN(B286/B285)</f>
-        <v/>
-      </c>
-      <c r="E286">
-        <f>LN(C286/C285)</f>
-        <v/>
+      <c r="D286" t="n">
+        <v>0.04488392507855975</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.06057086752727773</v>
       </c>
     </row>
     <row r="287">
@@ -6364,13 +5802,11 @@
       <c r="C287" t="n">
         <v>209.28</v>
       </c>
-      <c r="D287">
-        <f>LN(B287/B286)</f>
-        <v/>
-      </c>
-      <c r="E287">
-        <f>LN(C287/C286)</f>
-        <v/>
+      <c r="D287" t="n">
+        <v>0.0288035838304582</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-0.01895722786626637</v>
       </c>
     </row>
     <row r="288">
@@ -6383,13 +5819,11 @@
       <c r="C288" t="n">
         <v>205.35</v>
       </c>
-      <c r="D288">
-        <f>LN(B288/B287)</f>
-        <v/>
-      </c>
-      <c r="E288">
-        <f>LN(C288/C287)</f>
-        <v/>
+      <c r="D288" t="n">
+        <v>-0.004716848533125205</v>
+      </c>
+      <c r="E288" t="n">
+        <v>-0.03377561819358007</v>
       </c>
     </row>
     <row r="289">
@@ -6402,13 +5836,11 @@
       <c r="C289" t="n">
         <v>198.53</v>
       </c>
-      <c r="D289">
-        <f>LN(B289/B288)</f>
-        <v/>
-      </c>
-      <c r="E289">
-        <f>LN(C289/C288)</f>
-        <v/>
+      <c r="D289" t="n">
+        <v>0.05139064102052499</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0.06214938018602857</v>
       </c>
     </row>
     <row r="290">
@@ -6421,13 +5853,11 @@
       <c r="C290" t="n">
         <v>211.26</v>
       </c>
-      <c r="D290">
-        <f>LN(B290/B289)</f>
-        <v/>
-      </c>
-      <c r="E290">
-        <f>LN(C290/C289)</f>
-        <v/>
+      <c r="D290" t="n">
+        <v>-0.02645462576047172</v>
+      </c>
+      <c r="E290" t="n">
+        <v>-0.07870638614261041</v>
       </c>
     </row>
     <row r="291">
@@ -6440,13 +5870,11 @@
       <c r="C291" t="n">
         <v>195.27</v>
       </c>
-      <c r="D291">
-        <f>LN(B291/B290)</f>
-        <v/>
-      </c>
-      <c r="E291">
-        <f>LN(C291/C290)</f>
-        <v/>
+      <c r="D291" t="n">
+        <v>0.0185877402584977</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.02817514455288546</v>
       </c>
     </row>
     <row r="292">
@@ -6459,13 +5887,11 @@
       <c r="C292" t="n">
         <v>200.85</v>
       </c>
-      <c r="D292">
-        <f>LN(B292/B291)</f>
-        <v/>
-      </c>
-      <c r="E292">
-        <f>LN(C292/C291)</f>
-        <v/>
+      <c r="D292" t="n">
+        <v>0.01488772088097834</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0.01516939926256883</v>
       </c>
     </row>
     <row r="293">
@@ -6478,13 +5904,11 @@
       <c r="C293" t="n">
         <v>203.92</v>
       </c>
-      <c r="D293">
-        <f>LN(B293/B292)</f>
-        <v/>
-      </c>
-      <c r="E293">
-        <f>LN(C293/C292)</f>
-        <v/>
+      <c r="D293" t="n">
+        <v>-0.003905716839027833</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-0.03731981406339129</v>
       </c>
     </row>
     <row r="294">
@@ -6497,13 +5921,11 @@
       <c r="C294" t="n">
         <v>196.45</v>
       </c>
-      <c r="D294">
-        <f>LN(B294/B293)</f>
-        <v/>
-      </c>
-      <c r="E294">
-        <f>LN(C294/C293)</f>
-        <v/>
+      <c r="D294" t="n">
+        <v>-0.001528697698499086</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.02289696205460707</v>
       </c>
     </row>
     <row r="295">
@@ -6516,13 +5938,11 @@
       <c r="C295" t="n">
         <v>201</v>
       </c>
-      <c r="D295">
-        <f>LN(B295/B294)</f>
-        <v/>
-      </c>
-      <c r="E295">
-        <f>LN(C295/C294)</f>
-        <v/>
+      <c r="D295" t="n">
+        <v>0.03381123016203236</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.0003979307652987323</v>
       </c>
     </row>
     <row r="296">
@@ -6535,13 +5955,11 @@
       <c r="C296" t="n">
         <v>201.08</v>
       </c>
-      <c r="D296">
-        <f>LN(B296/B295)</f>
-        <v/>
-      </c>
-      <c r="E296">
-        <f>LN(C296/C295)</f>
-        <v/>
+      <c r="D296" t="n">
+        <v>0.0170701888859373</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.0601681584631011</v>
       </c>
     </row>
     <row r="297">
@@ -6554,13 +5972,11 @@
       <c r="C297" t="n">
         <v>213.55</v>
       </c>
-      <c r="D297">
-        <f>LN(B297/B296)</f>
-        <v/>
-      </c>
-      <c r="E297">
-        <f>LN(C297/C296)</f>
-        <v/>
+      <c r="D297" t="n">
+        <v>-0.003126223726266354</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-0.01125485733206005</v>
       </c>
     </row>
     <row r="298">
@@ -6573,13 +5989,11 @@
       <c r="C298" t="n">
         <v>211.16</v>
       </c>
-      <c r="D298">
-        <f>LN(B298/B297)</f>
-        <v/>
-      </c>
-      <c r="E298">
-        <f>LN(C298/C297)</f>
-        <v/>
+      <c r="D298" t="n">
+        <v>0.005899731524293387</v>
+      </c>
+      <c r="E298" t="n">
+        <v>9.471042295280977e-05</v>
       </c>
     </row>
     <row r="299">
@@ -6592,13 +6006,11 @@
       <c r="C299" t="n">
         <v>211.18</v>
       </c>
-      <c r="D299">
-        <f>LN(B299/B298)</f>
-        <v/>
-      </c>
-      <c r="E299">
-        <f>LN(C299/C298)</f>
-        <v/>
+      <c r="D299" t="n">
+        <v>0.01448143344992452</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0.01270425970216251</v>
       </c>
     </row>
     <row r="300">
@@ -6611,13 +6023,11 @@
       <c r="C300" t="n">
         <v>213.88</v>
       </c>
-      <c r="D300">
-        <f>LN(B300/B299)</f>
-        <v/>
-      </c>
-      <c r="E300">
-        <f>LN(C300/C299)</f>
-        <v/>
+      <c r="D300" t="n">
+        <v>-0.02386019192428506</v>
+      </c>
+      <c r="E300" t="n">
+        <v>-0.05526799177891691</v>
       </c>
     </row>
     <row r="301">
@@ -6630,13 +6040,11 @@
       <c r="C301" t="n">
         <v>202.38</v>
       </c>
-      <c r="D301">
-        <f>LN(B301/B300)</f>
-        <v/>
-      </c>
-      <c r="E301">
-        <f>LN(C301/C300)</f>
-        <v/>
+      <c r="D301" t="n">
+        <v>0.02398697143532075</v>
+      </c>
+      <c r="E301" t="n">
+        <v>0.1251021027415671</v>
       </c>
     </row>
     <row r="302">
@@ -6649,13 +6057,11 @@
       <c r="C302" t="n">
         <v>229.35</v>
       </c>
-      <c r="D302">
-        <f>LN(B302/B301)</f>
-        <v/>
-      </c>
-      <c r="E302">
-        <f>LN(C302/C301)</f>
-        <v/>
+      <c r="D302" t="n">
+        <v>0.009400929877436081</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.009719345830548298</v>
       </c>
     </row>
     <row r="303">
@@ -6668,13 +6074,11 @@
       <c r="C303" t="n">
         <v>231.59</v>
       </c>
-      <c r="D303">
-        <f>LN(B303/B302)</f>
-        <v/>
-      </c>
-      <c r="E303">
-        <f>LN(C303/C302)</f>
-        <v/>
+      <c r="D303" t="n">
+        <v>0.002649282984211211</v>
+      </c>
+      <c r="E303" t="n">
+        <v>-0.0166761239039472</v>
       </c>
     </row>
     <row r="304">
@@ -6687,13 +6091,11 @@
       <c r="C304" t="n">
         <v>227.76</v>
       </c>
-      <c r="D304">
-        <f>LN(B304/B303)</f>
-        <v/>
-      </c>
-      <c r="E304">
-        <f>LN(C304/C303)</f>
-        <v/>
+      <c r="D304" t="n">
+        <v>-0.001028840896591091</v>
+      </c>
+      <c r="E304" t="n">
+        <v>0.01904819497069441</v>
       </c>
     </row>
     <row r="305">
@@ -6706,13 +6108,11 @@
       <c r="C305" t="n">
         <v>232.14</v>
       </c>
-      <c r="D305">
-        <f>LN(B305/B304)</f>
-        <v/>
-      </c>
-      <c r="E305">
-        <f>LN(C305/C304)</f>
-        <v/>
+      <c r="D305" t="n">
+        <v>0.003282400395347566</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.03200578381442253</v>
       </c>
     </row>
     <row r="306">
@@ -6725,13 +6125,11 @@
       <c r="C306" t="n">
         <v>239.69</v>
       </c>
-      <c r="D306">
-        <f>LN(B306/B305)</f>
-        <v/>
-      </c>
-      <c r="E306">
-        <f>LN(C306/C305)</f>
-        <v/>
+      <c r="D306" t="n">
+        <v>0.01573454351934343</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-0.0237262058330861</v>
       </c>
     </row>
     <row r="307">
@@ -6744,13 +6142,11 @@
       <c r="C307" t="n">
         <v>234.07</v>
       </c>
-      <c r="D307">
-        <f>LN(B307/B306)</f>
-        <v/>
-      </c>
-      <c r="E307">
-        <f>LN(C307/C306)</f>
-        <v/>
+      <c r="D307" t="n">
+        <v>0.01208741643676649</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.04767673131276236</v>
       </c>
     </row>
     <row r="308">
@@ -6763,13 +6159,11 @@
       <c r="C308" t="n">
         <v>245.5</v>
       </c>
-      <c r="D308">
-        <f>LN(B308/B307)</f>
-        <v/>
-      </c>
-      <c r="E308">
-        <f>LN(C308/C307)</f>
-        <v/>
+      <c r="D308" t="n">
+        <v>-0.00310488780444765</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.03976889438005556</v>
       </c>
     </row>
     <row r="309">
@@ -6782,13 +6176,11 @@
       <c r="C309" t="n">
         <v>255.46</v>
       </c>
-      <c r="D309">
-        <f>LN(B309/B308)</f>
-        <v/>
-      </c>
-      <c r="E309">
-        <f>LN(C309/C308)</f>
-        <v/>
+      <c r="D309" t="n">
+        <v>0.01079243290452919</v>
+      </c>
+      <c r="E309" t="n">
+        <v>0.009971259682359611</v>
       </c>
     </row>
     <row r="310">
@@ -6801,13 +6193,11 @@
       <c r="C310" t="n">
         <v>258.02</v>
       </c>
-      <c r="D310">
-        <f>LN(B310/B309)</f>
-        <v/>
-      </c>
-      <c r="E310">
-        <f>LN(C310/C309)</f>
-        <v/>
+      <c r="D310" t="n">
+        <v>-0.02461328776482907</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-0.05067745673714508</v>
       </c>
     </row>
     <row r="311">
@@ -6820,13 +6210,11 @@
       <c r="C311" t="n">
         <v>245.27</v>
       </c>
-      <c r="D311">
-        <f>LN(B311/B310)</f>
-        <v/>
-      </c>
-      <c r="E311">
-        <f>LN(C311/C310)</f>
-        <v/>
+      <c r="D311" t="n">
+        <v>0.016873223114333</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.02821957494692876</v>
       </c>
     </row>
     <row r="312">
@@ -6839,13 +6227,11 @@
       <c r="C312" t="n">
         <v>252.29</v>
       </c>
-      <c r="D312">
-        <f>LN(B312/B311)</f>
-        <v/>
-      </c>
-      <c r="E312">
-        <f>LN(C312/C311)</f>
-        <v/>
+      <c r="D312" t="n">
+        <v>0.01897840057208134</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.04089016770871769</v>
       </c>
     </row>
     <row r="313">
@@ -6858,13 +6244,11 @@
       <c r="C313" t="n">
         <v>262.82</v>
       </c>
-      <c r="D313">
-        <f>LN(B313/B312)</f>
-        <v/>
-      </c>
-      <c r="E313">
-        <f>LN(C313/C312)</f>
-        <v/>
+      <c r="D313" t="n">
+        <v>0.007117164937330114</v>
+      </c>
+      <c r="E313" t="n">
+        <v>0.02832200405270948</v>
       </c>
     </row>
     <row r="314">
@@ -6877,13 +6261,11 @@
       <c r="C314" t="n">
         <v>270.37</v>
       </c>
-      <c r="D314">
-        <f>LN(B314/B313)</f>
-        <v/>
-      </c>
-      <c r="E314">
-        <f>LN(C314/C313)</f>
-        <v/>
+      <c r="D314" t="n">
+        <v>-0.0100589008237478</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-0.001221295094531675</v>
       </c>
     </row>
     <row r="315">
@@ -6917,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6932,6 +6314,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -6962,15 +6345,14 @@
           <t>Mean (Excel AVERAGE)</t>
         </is>
       </c>
-      <c r="B5" s="6">
-        <f>AVERAGE('Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>AVERAGE('Data &amp; Returns'!E3:E315)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B5" s="6" t="n">
+        <v>0.002503484702634983</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.004548139395955634</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -7001,13 +6383,11 @@
           <t>Manual: Σ(x - mean)²/N</t>
         </is>
       </c>
-      <c r="B9" s="6">
-        <f>SUMXMY2('Data &amp; Returns'!D3:D315,B5)/313</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>SUMXMY2('Data &amp; Returns'!E3:E315,C5)/313</f>
-        <v/>
+      <c r="B9" s="6" t="n">
+        <v>0.0007401755475323009</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.001672627746805722</v>
       </c>
     </row>
     <row r="10">
@@ -7016,13 +6396,11 @@
           <t>Excel VAR.P function</t>
         </is>
       </c>
-      <c r="B10" s="6">
-        <f>VAR.P('Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-      <c r="C10" s="6">
-        <f>VAR.P('Data &amp; Returns'!E3:E315)</f>
-        <v/>
+      <c r="B10" s="6" t="n">
+        <v>0.0007401755475323009</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.001672627746805722</v>
       </c>
     </row>
     <row r="11">
@@ -7040,6 +6418,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -7070,13 +6449,11 @@
           <t>Manual: SQRT(Variance)</t>
         </is>
       </c>
-      <c r="B15" s="6">
-        <f>SQRT(B9)</f>
-        <v/>
-      </c>
-      <c r="C15" s="6">
-        <f>SQRT(C9)</f>
-        <v/>
+      <c r="B15" s="6" t="n">
+        <v>0.02720616745394876</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.04089777190515056</v>
       </c>
     </row>
     <row r="16">
@@ -7085,13 +6462,11 @@
           <t>Excel STDEV.P function</t>
         </is>
       </c>
-      <c r="B16" s="6">
-        <f>STDEV.P('Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-      <c r="C16" s="6">
-        <f>STDEV.P('Data &amp; Returns'!E3:E315)</f>
-        <v/>
+      <c r="B16" s="6" t="n">
+        <v>0.02720616745394876</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.04089777190515056</v>
       </c>
     </row>
     <row r="17">
@@ -7109,6 +6484,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -7139,13 +6515,11 @@
           <t>Skewness</t>
         </is>
       </c>
-      <c r="B21" s="6">
-        <f>SKEW('Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-      <c r="C21" s="6">
-        <f>SKEW('Data &amp; Returns'!E3:E315)</f>
-        <v/>
+      <c r="B21" s="6" t="n">
+        <v>-0.8955974897245222</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-0.4944441746368287</v>
       </c>
     </row>
     <row r="22">
@@ -7154,15 +6528,14 @@
           <t>Kurtosis</t>
         </is>
       </c>
-      <c r="B22" s="6">
-        <f>KURT('Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-      <c r="C22" s="6">
-        <f>KURT('Data &amp; Returns'!E3:E315)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B22" s="6" t="n">
+        <v>6.695217061426991</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2.480645923665543</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -7193,13 +6566,11 @@
           <t>Weeks moving together (same sign)</t>
         </is>
       </c>
-      <c r="B26" s="6">
-        <f>SUMPRODUCT((SIGN('Data &amp; Returns'!D3:D315)=SIGN('Data &amp; Returns'!E3:E315))*1)</f>
-        <v/>
-      </c>
-      <c r="C26" s="6">
-        <f>B26/313</f>
-        <v/>
+      <c r="B26" s="6" t="n">
+        <v>254</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.8115015974440895</v>
       </c>
     </row>
     <row r="27">
@@ -7208,15 +6579,14 @@
           <t>Weeks moving apart (different sign)</t>
         </is>
       </c>
-      <c r="B27" s="6">
-        <f>SUMPRODUCT((SIGN('Data &amp; Returns'!D3:D315)&lt;&gt;SIGN('Data &amp; Returns'!E3:E315))*1)</f>
-        <v/>
-      </c>
-      <c r="C27" s="6">
-        <f>B27/313</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B27" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.1884984025559105</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
@@ -7242,9 +6612,8 @@
           <t>Manual: Σ(x-mean_x)(y-mean_y)/N</t>
         </is>
       </c>
-      <c r="B31" s="6">
-        <f>SUMPRODUCT(('Data &amp; Returns'!D3:D315-B5),('Data &amp; Returns'!E3:E315-C5))/313</f>
-        <v/>
+      <c r="B31" s="6" t="n">
+        <v>0.0008212995928398786</v>
       </c>
     </row>
     <row r="32">
@@ -7253,9 +6622,8 @@
           <t>Excel COVARIANCE.P function</t>
         </is>
       </c>
-      <c r="B32" s="6">
-        <f>COVARIANCE.P('Data &amp; Returns'!D3:D315,'Data &amp; Returns'!E3:E315)</f>
-        <v/>
+      <c r="B32" s="6" t="n">
+        <v>0.0008212995928398787</v>
       </c>
     </row>
     <row r="33">
@@ -7269,6 +6637,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -7294,9 +6663,8 @@
           <t>Manual: Cov(x,y)/(StdDev_x * StdDev_y)</t>
         </is>
       </c>
-      <c r="B37" s="6">
-        <f>B31/(B15*C15)</f>
-        <v/>
+      <c r="B37" s="6" t="n">
+        <v>0.738132949558889</v>
       </c>
     </row>
     <row r="38">
@@ -7305,9 +6673,8 @@
           <t>Excel CORREL function</t>
         </is>
       </c>
-      <c r="B38" s="6">
-        <f>CORREL('Data &amp; Returns'!D3:D315,'Data &amp; Returns'!E3:E315)</f>
-        <v/>
+      <c r="B38" s="6" t="n">
+        <v>0.7381329495588893</v>
       </c>
     </row>
     <row r="39">
@@ -7321,6 +6688,7 @@
         <v/>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -7346,9 +6714,8 @@
           <t>Slope (Beta)</t>
         </is>
       </c>
-      <c r="B43" s="6">
-        <f>SLOPE('Data &amp; Returns'!E3:E315,'Data &amp; Returns'!D3:D315)</f>
-        <v/>
+      <c r="B43" s="6" t="n">
+        <v>1.109601087982493</v>
       </c>
     </row>
     <row r="44">
@@ -7357,9 +6724,8 @@
           <t>Intercept (Alpha)</t>
         </is>
       </c>
-      <c r="B44" s="6">
-        <f>INTERCEPT('Data &amp; Returns'!E3:E315,'Data &amp; Returns'!D3:D315)</f>
-        <v/>
+      <c r="B44" s="6" t="n">
+        <v>0.001770270046164326</v>
       </c>
     </row>
     <row r="45">
@@ -7368,11 +6734,65 @@
           <t>R-Square</t>
         </is>
       </c>
-      <c r="B45" s="6">
-        <f>RSQ('Data &amp; Returns'!E3:E315,'Data &amp; Returns'!D3:D315)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B45" s="6" t="n">
+        <v>0.5448402512245055</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A29:E29"/>
@@ -7410,6 +6830,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -7438,9 +6859,8 @@
       <c r="A5" t="n">
         <v>-0.15</v>
       </c>
-      <c r="B5">
-        <f>COUNTIF('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A5)</f>
-        <v/>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7452,9 +6872,8 @@
       <c r="A6" t="n">
         <v>-0.14</v>
       </c>
-      <c r="B6">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A6,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A5)</f>
-        <v/>
+      <c r="B6" t="n">
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7466,9 +6885,8 @@
       <c r="A7" t="n">
         <v>-0.13</v>
       </c>
-      <c r="B7">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A7,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A6)</f>
-        <v/>
+      <c r="B7" t="n">
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7480,9 +6898,8 @@
       <c r="A8" t="n">
         <v>-0.12</v>
       </c>
-      <c r="B8">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A8,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A7)</f>
-        <v/>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7494,9 +6911,8 @@
       <c r="A9" t="n">
         <v>-0.11</v>
       </c>
-      <c r="B9">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A9,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A8)</f>
-        <v/>
+      <c r="B9" t="n">
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7508,9 +6924,8 @@
       <c r="A10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="B10">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A10,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A9)</f>
-        <v/>
+      <c r="B10" t="n">
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7522,9 +6937,8 @@
       <c r="A11" t="n">
         <v>-0.09</v>
       </c>
-      <c r="B11">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A11,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A10)</f>
-        <v/>
+      <c r="B11" t="n">
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7536,9 +6950,8 @@
       <c r="A12" t="n">
         <v>-0.08</v>
       </c>
-      <c r="B12">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A12,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A11)</f>
-        <v/>
+      <c r="B12" t="n">
+        <v>0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7550,9 +6963,8 @@
       <c r="A13" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="B13">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A13,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A12)</f>
-        <v/>
+      <c r="B13" t="n">
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7564,9 +6976,8 @@
       <c r="A14" t="n">
         <v>-0.06</v>
       </c>
-      <c r="B14">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A14,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A13)</f>
-        <v/>
+      <c r="B14" t="n">
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7578,9 +6989,8 @@
       <c r="A15" t="n">
         <v>-0.05</v>
       </c>
-      <c r="B15">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A15,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A14)</f>
-        <v/>
+      <c r="B15" t="n">
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7592,9 +7002,8 @@
       <c r="A16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="B16">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A16,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A15)</f>
-        <v/>
+      <c r="B16" t="n">
+        <v>6</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7606,9 +7015,8 @@
       <c r="A17" t="n">
         <v>-0.03</v>
       </c>
-      <c r="B17">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A17,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A16)</f>
-        <v/>
+      <c r="B17" t="n">
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7620,9 +7028,8 @@
       <c r="A18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="B18">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A18,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A17)</f>
-        <v/>
+      <c r="B18" t="n">
+        <v>29</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7634,9 +7041,8 @@
       <c r="A19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="B19">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A19,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A18)</f>
-        <v/>
+      <c r="B19" t="n">
+        <v>31</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7648,9 +7054,8 @@
       <c r="A20" t="n">
         <v>0</v>
       </c>
-      <c r="B20">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A20,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A19)</f>
-        <v/>
+      <c r="B20" t="n">
+        <v>53</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7662,9 +7067,8 @@
       <c r="A21" t="n">
         <v>0.01</v>
       </c>
-      <c r="B21">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A21,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A20)</f>
-        <v/>
+      <c r="B21" t="n">
+        <v>57</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7676,9 +7080,8 @@
       <c r="A22" t="n">
         <v>0.02</v>
       </c>
-      <c r="B22">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A22,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A21)</f>
-        <v/>
+      <c r="B22" t="n">
+        <v>68</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7690,9 +7093,8 @@
       <c r="A23" t="n">
         <v>0.03</v>
       </c>
-      <c r="B23">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A23,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A22)</f>
-        <v/>
+      <c r="B23" t="n">
+        <v>23</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7704,9 +7106,8 @@
       <c r="A24" t="n">
         <v>0.04</v>
       </c>
-      <c r="B24">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A24,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A23)</f>
-        <v/>
+      <c r="B24" t="n">
+        <v>14</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7718,9 +7119,8 @@
       <c r="A25" t="n">
         <v>0.05</v>
       </c>
-      <c r="B25">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A25,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A24)</f>
-        <v/>
+      <c r="B25" t="n">
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7732,9 +7132,8 @@
       <c r="A26" t="n">
         <v>0.06</v>
       </c>
-      <c r="B26">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A26,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A25)</f>
-        <v/>
+      <c r="B26" t="n">
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7746,9 +7145,8 @@
       <c r="A27" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B27">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A27,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A26)</f>
-        <v/>
+      <c r="B27" t="n">
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7760,9 +7158,8 @@
       <c r="A28" t="n">
         <v>0.08</v>
       </c>
-      <c r="B28">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A28,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A27)</f>
-        <v/>
+      <c r="B28" t="n">
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7774,9 +7171,8 @@
       <c r="A29" t="n">
         <v>0.09</v>
       </c>
-      <c r="B29">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A29,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A28)</f>
-        <v/>
+      <c r="B29" t="n">
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7788,9 +7184,8 @@
       <c r="A30" t="n">
         <v>0.1</v>
       </c>
-      <c r="B30">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A30,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A29)</f>
-        <v/>
+      <c r="B30" t="n">
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7802,9 +7197,8 @@
       <c r="A31" t="n">
         <v>0.11</v>
       </c>
-      <c r="B31">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A31,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A30)</f>
-        <v/>
+      <c r="B31" t="n">
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7816,9 +7210,8 @@
       <c r="A32" t="n">
         <v>0.12</v>
       </c>
-      <c r="B32">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A32,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A31)</f>
-        <v/>
+      <c r="B32" t="n">
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7830,9 +7223,8 @@
       <c r="A33" t="n">
         <v>0.13</v>
       </c>
-      <c r="B33">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A33,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A32)</f>
-        <v/>
+      <c r="B33" t="n">
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7844,9 +7236,8 @@
       <c r="A34" t="n">
         <v>0.14</v>
       </c>
-      <c r="B34">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A34,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A33)</f>
-        <v/>
+      <c r="B34" t="n">
+        <v>0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7858,9 +7249,8 @@
       <c r="A35" t="n">
         <v>0.15</v>
       </c>
-      <c r="B35">
-        <f>COUNTIFS('Data &amp; Returns'!$D$3:$D$315,"&lt;="&amp;A35,'Data &amp; Returns'!$D$3:$D$315,"&gt;"&amp;A34)</f>
-        <v/>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7868,6 +7258,8 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -7896,9 +7288,8 @@
       <c r="A40" t="n">
         <v>-0.2</v>
       </c>
-      <c r="B40">
-        <f>COUNTIF('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A40)</f>
-        <v/>
+      <c r="B40" t="n">
+        <v>0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7910,9 +7301,8 @@
       <c r="A41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="B41">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A41,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A40)</f>
-        <v/>
+      <c r="B41" t="n">
+        <v>1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7924,9 +7314,8 @@
       <c r="A42" t="n">
         <v>-0.18</v>
       </c>
-      <c r="B42">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A42,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A41)</f>
-        <v/>
+      <c r="B42" t="n">
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7938,9 +7327,8 @@
       <c r="A43" t="n">
         <v>-0.17</v>
       </c>
-      <c r="B43">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A43,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A42)</f>
-        <v/>
+      <c r="B43" t="n">
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7952,9 +7340,8 @@
       <c r="A44" t="n">
         <v>-0.16</v>
       </c>
-      <c r="B44">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A44,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A43)</f>
-        <v/>
+      <c r="B44" t="n">
+        <v>0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7966,9 +7353,8 @@
       <c r="A45" t="n">
         <v>-0.15</v>
       </c>
-      <c r="B45">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A45,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A44)</f>
-        <v/>
+      <c r="B45" t="n">
+        <v>0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -7980,9 +7366,8 @@
       <c r="A46" t="n">
         <v>-0.14</v>
       </c>
-      <c r="B46">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A46,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A45)</f>
-        <v/>
+      <c r="B46" t="n">
+        <v>1</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7994,9 +7379,8 @@
       <c r="A47" t="n">
         <v>-0.13</v>
       </c>
-      <c r="B47">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A47,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A46)</f>
-        <v/>
+      <c r="B47" t="n">
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -8008,9 +7392,8 @@
       <c r="A48" t="n">
         <v>-0.12</v>
       </c>
-      <c r="B48">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A48,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A47)</f>
-        <v/>
+      <c r="B48" t="n">
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -8022,9 +7405,8 @@
       <c r="A49" t="n">
         <v>-0.11</v>
       </c>
-      <c r="B49">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A49,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A48)</f>
-        <v/>
+      <c r="B49" t="n">
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -8036,9 +7418,8 @@
       <c r="A50" t="n">
         <v>-0.1</v>
       </c>
-      <c r="B50">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A50,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A49)</f>
-        <v/>
+      <c r="B50" t="n">
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -8050,9 +7431,8 @@
       <c r="A51" t="n">
         <v>-0.09</v>
       </c>
-      <c r="B51">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A51,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A50)</f>
-        <v/>
+      <c r="B51" t="n">
+        <v>0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -8064,9 +7444,8 @@
       <c r="A52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="B52">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A52,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A51)</f>
-        <v/>
+      <c r="B52" t="n">
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -8078,9 +7457,8 @@
       <c r="A53" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="B53">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A53,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A52)</f>
-        <v/>
+      <c r="B53" t="n">
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -8092,9 +7470,8 @@
       <c r="A54" t="n">
         <v>-0.06</v>
       </c>
-      <c r="B54">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A54,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A53)</f>
-        <v/>
+      <c r="B54" t="n">
+        <v>7</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8106,9 +7483,8 @@
       <c r="A55" t="n">
         <v>-0.05</v>
       </c>
-      <c r="B55">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A55,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A54)</f>
-        <v/>
+      <c r="B55" t="n">
+        <v>8</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8120,9 +7496,8 @@
       <c r="A56" t="n">
         <v>-0.04</v>
       </c>
-      <c r="B56">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A56,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A55)</f>
-        <v/>
+      <c r="B56" t="n">
+        <v>8</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8134,9 +7509,8 @@
       <c r="A57" t="n">
         <v>-0.03</v>
       </c>
-      <c r="B57">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A57,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A56)</f>
-        <v/>
+      <c r="B57" t="n">
+        <v>19</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8148,9 +7522,8 @@
       <c r="A58" t="n">
         <v>-0.02</v>
       </c>
-      <c r="B58">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A58,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A57)</f>
-        <v/>
+      <c r="B58" t="n">
+        <v>24</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8162,9 +7535,8 @@
       <c r="A59" t="n">
         <v>-0.01</v>
       </c>
-      <c r="B59">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A59,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A58)</f>
-        <v/>
+      <c r="B59" t="n">
+        <v>25</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8176,9 +7548,8 @@
       <c r="A60" t="n">
         <v>0</v>
       </c>
-      <c r="B60">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A60,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A59)</f>
-        <v/>
+      <c r="B60" t="n">
+        <v>32</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8190,9 +7561,8 @@
       <c r="A61" t="n">
         <v>0.01</v>
       </c>
-      <c r="B61">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A61,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A60)</f>
-        <v/>
+      <c r="B61" t="n">
+        <v>44</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8204,9 +7574,8 @@
       <c r="A62" t="n">
         <v>0.02</v>
       </c>
-      <c r="B62">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A62,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A61)</f>
-        <v/>
+      <c r="B62" t="n">
+        <v>28</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8218,9 +7587,8 @@
       <c r="A63" t="n">
         <v>0.03</v>
       </c>
-      <c r="B63">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A63,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A62)</f>
-        <v/>
+      <c r="B63" t="n">
+        <v>37</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8232,9 +7600,8 @@
       <c r="A64" t="n">
         <v>0.04</v>
       </c>
-      <c r="B64">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A64,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A63)</f>
-        <v/>
+      <c r="B64" t="n">
+        <v>21</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8246,9 +7613,8 @@
       <c r="A65" t="n">
         <v>0.05</v>
       </c>
-      <c r="B65">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A65,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A64)</f>
-        <v/>
+      <c r="B65" t="n">
+        <v>14</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8260,9 +7626,8 @@
       <c r="A66" t="n">
         <v>0.06</v>
       </c>
-      <c r="B66">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A66,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A65)</f>
-        <v/>
+      <c r="B66" t="n">
+        <v>14</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8274,9 +7639,8 @@
       <c r="A67" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B67">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A67,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A66)</f>
-        <v/>
+      <c r="B67" t="n">
+        <v>6</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8288,9 +7652,8 @@
       <c r="A68" t="n">
         <v>0.08</v>
       </c>
-      <c r="B68">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A68,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A67)</f>
-        <v/>
+      <c r="B68" t="n">
+        <v>10</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8302,9 +7665,8 @@
       <c r="A69" t="n">
         <v>0.09</v>
       </c>
-      <c r="B69">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A69,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A68)</f>
-        <v/>
+      <c r="B69" t="n">
+        <v>3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8316,9 +7678,8 @@
       <c r="A70" t="n">
         <v>0.1</v>
       </c>
-      <c r="B70">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A70,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A69)</f>
-        <v/>
+      <c r="B70" t="n">
+        <v>0</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8330,9 +7691,8 @@
       <c r="A71" t="n">
         <v>0.11</v>
       </c>
-      <c r="B71">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A71,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A70)</f>
-        <v/>
+      <c r="B71" t="n">
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8344,9 +7704,8 @@
       <c r="A72" t="n">
         <v>0.12</v>
       </c>
-      <c r="B72">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A72,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A71)</f>
-        <v/>
+      <c r="B72" t="n">
+        <v>0</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8358,9 +7717,8 @@
       <c r="A73" t="n">
         <v>0.13</v>
       </c>
-      <c r="B73">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A73,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A72)</f>
-        <v/>
+      <c r="B73" t="n">
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8372,9 +7730,8 @@
       <c r="A74" t="n">
         <v>0.14</v>
       </c>
-      <c r="B74">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A74,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A73)</f>
-        <v/>
+      <c r="B74" t="n">
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8386,9 +7743,8 @@
       <c r="A75" t="n">
         <v>0.15</v>
       </c>
-      <c r="B75">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A75,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A74)</f>
-        <v/>
+      <c r="B75" t="n">
+        <v>0</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8400,9 +7756,8 @@
       <c r="A76" t="n">
         <v>0.16</v>
       </c>
-      <c r="B76">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A76,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A75)</f>
-        <v/>
+      <c r="B76" t="n">
+        <v>0</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8414,9 +7769,8 @@
       <c r="A77" t="n">
         <v>0.17</v>
       </c>
-      <c r="B77">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A77,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A76)</f>
-        <v/>
+      <c r="B77" t="n">
+        <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8428,9 +7782,8 @@
       <c r="A78" t="n">
         <v>0.18</v>
       </c>
-      <c r="B78">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A78,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A77)</f>
-        <v/>
+      <c r="B78" t="n">
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8442,9 +7795,8 @@
       <c r="A79" t="n">
         <v>0.19</v>
       </c>
-      <c r="B79">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A79,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A78)</f>
-        <v/>
+      <c r="B79" t="n">
+        <v>0</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8456,9 +7808,8 @@
       <c r="A80" t="n">
         <v>0.2</v>
       </c>
-      <c r="B80">
-        <f>COUNTIFS('Data &amp; Returns'!$E$3:$E$315,"&lt;="&amp;A80,'Data &amp; Returns'!$E$3:$E$315,"&gt;"&amp;A79)</f>
-        <v/>
+      <c r="B80" t="n">
+        <v>0</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8483,7 +7834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8603,13 +7954,11 @@
           <t>Mean Weekly Return</t>
         </is>
       </c>
-      <c r="B12" s="11">
-        <f>Calculations!B6</f>
-        <v/>
-      </c>
-      <c r="C12" s="11">
-        <f>Calculations!C6</f>
-        <v/>
+      <c r="B12" s="11" t="n">
+        <v>0.002503484702634983</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0.004548139395955634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8623,13 +7972,11 @@
           <t>Variance</t>
         </is>
       </c>
-      <c r="B13" s="12">
-        <f>Calculations!B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="12">
-        <f>Calculations!C12</f>
-        <v/>
+      <c r="B13" s="12" t="n">
+        <v>0.0007401755475323009</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>0.001672627746805722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8643,13 +7990,11 @@
           <t>Standard Deviation</t>
         </is>
       </c>
-      <c r="B14" s="12">
-        <f>Calculations!B20</f>
-        <v/>
-      </c>
-      <c r="C14" s="12">
-        <f>Calculations!C20</f>
-        <v/>
+      <c r="B14" s="12" t="n">
+        <v>0.02720616745394876</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.04089777190515056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8663,13 +8008,11 @@
           <t>Skewness</t>
         </is>
       </c>
-      <c r="B15" s="12">
-        <f>Calculations!B28</f>
-        <v/>
-      </c>
-      <c r="C15" s="12">
-        <f>Calculations!C28</f>
-        <v/>
+      <c r="B15" s="12" t="n">
+        <v>-0.8955974897245222</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>-0.4944441746368287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -8683,13 +8026,11 @@
           <t>Kurtosis</t>
         </is>
       </c>
-      <c r="B16" s="12">
-        <f>Calculations!B29</f>
-        <v/>
-      </c>
-      <c r="C16" s="12">
-        <f>Calculations!C29</f>
-        <v/>
+      <c r="B16" s="12" t="n">
+        <v>6.695217061426991</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>2.480645923665543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -8703,9 +8044,8 @@
           <t>Covariance</t>
         </is>
       </c>
-      <c r="B17" s="12">
-        <f>Calculations!B36</f>
-        <v/>
+      <c r="B17" s="12" t="n">
+        <v>0.0008212995928398786</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -8719,9 +8059,8 @@
           <t>Correlation</t>
         </is>
       </c>
-      <c r="B18" s="12">
-        <f>Calculations!B42</f>
-        <v/>
+      <c r="B18" s="12" t="n">
+        <v>0.7381329495588893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -8735,13 +8074,11 @@
           <t>Weeks Moving Together</t>
         </is>
       </c>
-      <c r="B19" s="12">
-        <f>Calculations!B32</f>
-        <v/>
-      </c>
-      <c r="C19" s="12">
-        <f>Calculations!C32</f>
-        <v/>
+      <c r="B19" s="12" t="n">
+        <v>254</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>0.8115015974440895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -8755,13 +8092,11 @@
           <t>Weeks Moving Apart</t>
         </is>
       </c>
-      <c r="B20" s="12">
-        <f>Calculations!B33</f>
-        <v/>
-      </c>
-      <c r="C20" s="12">
-        <f>Calculations!C33</f>
-        <v/>
+      <c r="B20" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0.1884984025559105</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8800,9 +8135,8 @@
           <t>Beta (Slope)</t>
         </is>
       </c>
-      <c r="B24" s="12">
-        <f>Calculations!B48</f>
-        <v/>
+      <c r="B24" s="12" t="n">
+        <v>1.109601087982493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -8816,9 +8150,8 @@
           <t>Alpha (Intercept)</t>
         </is>
       </c>
-      <c r="B25" s="12">
-        <f>Calculations!B49</f>
-        <v/>
+      <c r="B25" s="12" t="n">
+        <v>0.001770270046164326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -8832,9 +8165,8 @@
           <t>R-Square</t>
         </is>
       </c>
-      <c r="B26" s="12">
-        <f>Calculations!B50</f>
-        <v/>
+      <c r="B26" s="12" t="n">
+        <v>0.5448402512245055</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8843,6 +8175,79 @@
       </c>
     </row>
     <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>

--- a/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
+++ b/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
@@ -6299,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6314,7 +6314,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -6345,14 +6344,15 @@
           <t>Mean (Excel AVERAGE)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>0.002503484702634983</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.004548139395955634</v>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="B5" s="6">
+        <f>AVERAGE('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C5" s="6">
+        <f>AVERAGE('Data &amp; Returns'!E2:E315)</f>
+        <v/>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -6383,11 +6383,13 @@
           <t>Manual: Σ(x - mean)²/N</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>0.0007401755475323009</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0.001672627746805722</v>
+      <c r="B9" s="6">
+        <f>VAR.P('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C9" s="6">
+        <f>VAR.P('Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -6396,11 +6398,13 @@
           <t>Excel VAR.P function</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>0.0007401755475323009</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0.001672627746805722</v>
+      <c r="B10" s="6">
+        <f>VAR.P('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C10" s="6">
+        <f>VAR.P('Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -6418,7 +6422,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
@@ -6449,11 +6452,13 @@
           <t>Manual: SQRT(Variance)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>0.02720616745394876</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0.04089777190515056</v>
+      <c r="B15" s="6">
+        <f>STDEV.P('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>STDEV.P('Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -6462,11 +6467,13 @@
           <t>Excel STDEV.P function</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>0.02720616745394876</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>0.04089777190515056</v>
+      <c r="B16" s="6">
+        <f>STDEV.P('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C16" s="6">
+        <f>STDEV.P('Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -6484,7 +6491,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
@@ -6515,11 +6521,13 @@
           <t>Skewness</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
-        <v>-0.8955974897245222</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>-0.4944441746368287</v>
+      <c r="B21" s="6">
+        <f>SKEW.P('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C21" s="6">
+        <f>SKEW.P('Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -6528,14 +6536,15 @@
           <t>Kurtosis</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>6.695217061426991</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>2.480645923665543</v>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="B22" s="6">
+        <f>KURT('Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+      <c r="C22" s="6">
+        <f>KURT('Data &amp; Returns'!E2:E315)</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -6566,11 +6575,13 @@
           <t>Weeks moving together (same sign)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>254</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>0.8115015974440895</v>
+      <c r="B26" s="6">
+        <f>SUMPRODUCT(('Data &amp; Returns'!D2:D315&gt;0)*('Data &amp; Returns'!E2:E315&gt;0))+SUMPRODUCT(('Data &amp; Returns'!D2:D315&lt;0)*('Data &amp; Returns'!E2:E315&lt;0))</f>
+        <v/>
+      </c>
+      <c r="C26" s="6">
+        <f>B26/(B26+B27)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -6579,14 +6590,15 @@
           <t>Weeks moving apart (different sign)</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>0.1884984025559105</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="B27" s="6">
+        <f>SUMPRODUCT(('Data &amp; Returns'!D2:D315&gt;0)*('Data &amp; Returns'!E2:E315&lt;0))+SUMPRODUCT(('Data &amp; Returns'!D2:D315&lt;0)*('Data &amp; Returns'!E2:E315&gt;0))</f>
+        <v/>
+      </c>
+      <c r="C27" s="6">
+        <f>B27/(B26+B27)</f>
+        <v/>
+      </c>
+    </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
@@ -6612,8 +6624,9 @@
           <t>Manual: Σ(x-mean_x)(y-mean_y)/N</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>0.0008212995928398786</v>
+      <c r="B31" s="6">
+        <f>COVARIANCE.P('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -6622,8 +6635,9 @@
           <t>Excel COVARIANCE.P function</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
-        <v>0.0008212995928398787</v>
+      <c r="B32" s="6">
+        <f>COVARIANCE.P('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -6637,7 +6651,6 @@
         <v/>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -6663,8 +6676,9 @@
           <t>Manual: Cov(x,y)/(StdDev_x * StdDev_y)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
-        <v>0.738132949558889</v>
+      <c r="B37" s="6">
+        <f>CORREL('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -6673,8 +6687,9 @@
           <t>Excel CORREL function</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
-        <v>0.7381329495588893</v>
+      <c r="B38" s="6">
+        <f>CORREL('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6688,7 +6703,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
@@ -6714,8 +6728,9 @@
           <t>Slope (Beta)</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n">
-        <v>1.109601087982493</v>
+      <c r="B43" s="6">
+        <f>SLOPE('Data &amp; Returns'!E2:E315,'Data &amp; Returns'!D2:D315)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -6724,8 +6739,9 @@
           <t>Intercept (Alpha)</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n">
-        <v>0.001770270046164326</v>
+      <c r="B44" s="6">
+        <f>INTERCEPT('Data &amp; Returns'!E2:E315,'Data &amp; Returns'!D2:D315)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -6734,65 +6750,11 @@
           <t>R-Square</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n">
-        <v>0.5448402512245055</v>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
+      <c r="B45" s="6">
+        <f>RSQ('Data &amp; Returns'!E2:E315,'Data &amp; Returns'!D2:D315)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A29:E29"/>
@@ -6830,7 +6792,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -7258,8 +7219,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
@@ -7834,7 +7793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7850,7 +7809,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -7918,7 +7876,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
@@ -7954,11 +7911,13 @@
           <t>Mean Weekly Return</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>0.002503484702634983</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>0.004548139395955634</v>
+      <c r="B12" s="11">
+        <f>Calculations!B5</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>Calculations!C5</f>
+        <v/>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -7972,11 +7931,13 @@
           <t>Variance</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>0.0007401755475323009</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0.001672627746805722</v>
+      <c r="B13" s="12">
+        <f>Calculations!B10</f>
+        <v/>
+      </c>
+      <c r="C13" s="12">
+        <f>Calculations!C10</f>
+        <v/>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -7990,11 +7951,13 @@
           <t>Standard Deviation</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>0.02720616745394876</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0.04089777190515056</v>
+      <c r="B14" s="12">
+        <f>Calculations!B16</f>
+        <v/>
+      </c>
+      <c r="C14" s="12">
+        <f>Calculations!C16</f>
+        <v/>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -8008,11 +7971,13 @@
           <t>Skewness</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>-0.8955974897245222</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>-0.4944441746368287</v>
+      <c r="B15" s="12">
+        <f>Calculations!B21</f>
+        <v/>
+      </c>
+      <c r="C15" s="12">
+        <f>Calculations!C21</f>
+        <v/>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -8026,11 +7991,13 @@
           <t>Kurtosis</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>6.695217061426991</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>2.480645923665543</v>
+      <c r="B16" s="12">
+        <f>Calculations!B22</f>
+        <v/>
+      </c>
+      <c r="C16" s="12">
+        <f>Calculations!C22</f>
+        <v/>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -8044,8 +8011,9 @@
           <t>Covariance</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>0.0008212995928398786</v>
+      <c r="B17" s="12">
+        <f>Calculations!B32</f>
+        <v/>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -8059,8 +8027,9 @@
           <t>Correlation</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>0.7381329495588893</v>
+      <c r="B18" s="12">
+        <f>Calculations!B38</f>
+        <v/>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -8074,11 +8043,13 @@
           <t>Weeks Moving Together</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>254</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>0.8115015974440895</v>
+      <c r="B19" s="12">
+        <f>Calculations!B26</f>
+        <v/>
+      </c>
+      <c r="C19" s="12">
+        <f>Calculations!C26</f>
+        <v/>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -8092,11 +8063,13 @@
           <t>Weeks Moving Apart</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>0.1884984025559105</v>
+      <c r="B20" s="12">
+        <f>Calculations!B27</f>
+        <v/>
+      </c>
+      <c r="C20" s="12">
+        <f>Calculations!C27</f>
+        <v/>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -8104,7 +8077,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
@@ -8135,8 +8107,9 @@
           <t>Beta (Slope)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>1.109601087982493</v>
+      <c r="B24" s="12">
+        <f>Calculations!B43</f>
+        <v/>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -8150,8 +8123,9 @@
           <t>Alpha (Intercept)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>0.001770270046164326</v>
+      <c r="B25" s="12">
+        <f>Calculations!B44</f>
+        <v/>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -8165,8 +8139,9 @@
           <t>R-Square</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>0.5448402512245055</v>
+      <c r="B26" s="12">
+        <f>Calculations!B45</f>
+        <v/>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8174,80 +8149,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>

--- a/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
+++ b/Principles of Finance with Excel, Individual Report 2000w/Q2_Analysis.xlsx
@@ -6384,11 +6384,11 @@
         </is>
       </c>
       <c r="B9" s="6">
-        <f>VAR.P('Data &amp; Returns'!D2:D315)</f>
+        <f>SUMPRODUCT(('Data &amp; Returns'!D2:D315-B5)^2)/COUNTA('Data &amp; Returns'!D2:D315)</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>VAR.P('Data &amp; Returns'!E2:E315)</f>
+        <f>SUMPRODUCT(('Data &amp; Returns'!E2:E315-C5)^2)/COUNTA('Data &amp; Returns'!E2:E315)</f>
         <v/>
       </c>
     </row>
@@ -6453,11 +6453,11 @@
         </is>
       </c>
       <c r="B15" s="6">
-        <f>STDEV.P('Data &amp; Returns'!D2:D315)</f>
+        <f>SQRT(B9)</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>STDEV.P('Data &amp; Returns'!E2:E315)</f>
+        <f>SQRT(C9)</f>
         <v/>
       </c>
     </row>
@@ -6522,11 +6522,11 @@
         </is>
       </c>
       <c r="B21" s="6">
-        <f>SKEW.P('Data &amp; Returns'!D2:D315)</f>
+        <f>SKEW('Data &amp; Returns'!D2:D315)</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>SKEW.P('Data &amp; Returns'!E2:E315)</f>
+        <f>SKEW('Data &amp; Returns'!E2:E315)</f>
         <v/>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="B31" s="6">
-        <f>COVARIANCE.P('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <f>SUMPRODUCT(('Data &amp; Returns'!D2:D315-B5)*('Data &amp; Returns'!E2:E315-C5))/COUNTA('Data &amp; Returns'!D2:D315)</f>
         <v/>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="B37" s="6">
-        <f>CORREL('Data &amp; Returns'!D2:D315,'Data &amp; Returns'!E2:E315)</f>
+        <f>B32/(B16*C16)</f>
         <v/>
       </c>
     </row>
